--- a/Zmanim_Last_Current_Year_Milwaukee.xlsx
+++ b/Zmanim_Last_Current_Year_Milwaukee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\APosner\Downloads\torah-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B1EDF1-E90B-4784-8F30-CBE7B4042AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4631631-2956-4B25-9F65-6EEA8F90D7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="52380" yWindow="780" windowWidth="38700" windowHeight="15345" xr2:uid="{6223D559-8CF2-4D99-8677-49497ED3520A}"/>
   </bookViews>
@@ -220,11 +220,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -324,13 +323,13 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -395,10 +394,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32CC990B-8605-45D6-93F5-F304EF34B798}" name="Last_Current_Next" displayName="Last_Current_Next" ref="A1:AK182" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:AK182" xr:uid="{32CC990B-8605-45D6-93F5-F304EF34B798}"/>
   <tableColumns count="37">
-    <tableColumn id="1" xr3:uid="{5534E0B6-2BF0-4C6E-AF09-4BB532A12126}" uniqueName="1" name="date" queryTableFieldId="1" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{978B3185-C87E-41AA-A3FC-BAE7B910BD22}" uniqueName="2" name="title" queryTableFieldId="2" dataDxfId="33"/>
-    <tableColumn id="31" xr3:uid="{484FAFE2-E2D4-484C-9611-0253F74A99FD}" uniqueName="31" name="city" queryTableFieldId="31" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{FB8A712F-DD72-4EEE-91A6-CDE0174D2EB6}" uniqueName="3" name="tzid" queryTableFieldId="3" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{5534E0B6-2BF0-4C6E-AF09-4BB532A12126}" uniqueName="1" name="date" queryTableFieldId="1" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{978B3185-C87E-41AA-A3FC-BAE7B910BD22}" uniqueName="2" name="title" queryTableFieldId="2" dataDxfId="32"/>
+    <tableColumn id="31" xr3:uid="{484FAFE2-E2D4-484C-9611-0253F74A99FD}" uniqueName="31" name="city" queryTableFieldId="31" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{FB8A712F-DD72-4EEE-91A6-CDE0174D2EB6}" uniqueName="3" name="tzid" queryTableFieldId="3" dataDxfId="30"/>
     <tableColumn id="4" xr3:uid="{D9D6EE09-0412-4CAC-83C4-759E38A043FC}" uniqueName="4" name="latitude" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{9E02AEA1-04D3-413E-9B6F-82772FDD6C91}" uniqueName="5" name="longitude" queryTableFieldId="5"/>
     <tableColumn id="32" xr3:uid="{5DBE150B-83A1-4A32-8A3C-5F4CE97788B1}" uniqueName="32" name="cc" queryTableFieldId="32" dataDxfId="29"/>
@@ -890,7 +889,7 @@
       <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>38</v>
       </c>
       <c r="D2" t="s">
@@ -902,25 +901,25 @@
       <c r="F2">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
         <v>40</v>
       </c>
       <c r="K2">
         <v>53216</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="L2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s">
         <v>43</v>
       </c>
       <c r="N2" s="2">
@@ -1003,7 +1002,7 @@
       <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>38</v>
       </c>
       <c r="D3" t="s">
@@ -1015,25 +1014,25 @@
       <c r="F3">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
         <v>40</v>
       </c>
       <c r="K3">
         <v>53216</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="3" t="s">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
         <v>43</v>
       </c>
       <c r="N3" s="2">
@@ -1116,7 +1115,7 @@
       <c r="B4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>38</v>
       </c>
       <c r="D4" t="s">
@@ -1128,25 +1127,25 @@
       <c r="F4">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
         <v>40</v>
       </c>
       <c r="K4">
         <v>53216</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
         <v>43</v>
       </c>
       <c r="N4" s="2">
@@ -1229,7 +1228,7 @@
       <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>38</v>
       </c>
       <c r="D5" t="s">
@@ -1241,25 +1240,25 @@
       <c r="F5">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
         <v>40</v>
       </c>
       <c r="K5">
         <v>53216</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" t="s">
         <v>43</v>
       </c>
       <c r="N5" s="2">
@@ -1342,7 +1341,7 @@
       <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>38</v>
       </c>
       <c r="D6" t="s">
@@ -1354,25 +1353,25 @@
       <c r="F6">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
         <v>40</v>
       </c>
       <c r="K6">
         <v>53216</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" s="3" t="s">
+      <c r="L6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" t="s">
         <v>43</v>
       </c>
       <c r="N6" s="2">
@@ -1455,7 +1454,7 @@
       <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>38</v>
       </c>
       <c r="D7" t="s">
@@ -1467,25 +1466,25 @@
       <c r="F7">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
         <v>40</v>
       </c>
       <c r="K7">
         <v>53216</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="L7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" t="s">
         <v>43</v>
       </c>
       <c r="N7" s="2">
@@ -1568,7 +1567,7 @@
       <c r="B8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>38</v>
       </c>
       <c r="D8" t="s">
@@ -1580,25 +1579,25 @@
       <c r="F8">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
         <v>40</v>
       </c>
       <c r="K8">
         <v>53216</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="3" t="s">
+      <c r="L8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" t="s">
         <v>43</v>
       </c>
       <c r="N8" s="2">
@@ -1681,7 +1680,7 @@
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
@@ -1693,25 +1692,25 @@
       <c r="F9">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="I9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" t="s">
         <v>40</v>
       </c>
       <c r="K9">
         <v>53216</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" t="s">
         <v>43</v>
       </c>
       <c r="N9" s="2">
@@ -1794,7 +1793,7 @@
       <c r="B10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>38</v>
       </c>
       <c r="D10" t="s">
@@ -1806,25 +1805,25 @@
       <c r="F10">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="I10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s">
         <v>40</v>
       </c>
       <c r="K10">
         <v>53216</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" t="s">
         <v>43</v>
       </c>
       <c r="N10" s="2">
@@ -1907,7 +1906,7 @@
       <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>38</v>
       </c>
       <c r="D11" t="s">
@@ -1919,25 +1918,25 @@
       <c r="F11">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="I11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" t="s">
         <v>40</v>
       </c>
       <c r="K11">
         <v>53216</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="L11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" t="s">
         <v>43</v>
       </c>
       <c r="N11" s="2">
@@ -2020,7 +2019,7 @@
       <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>38</v>
       </c>
       <c r="D12" t="s">
@@ -2032,25 +2031,25 @@
       <c r="F12">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="I12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" t="s">
         <v>40</v>
       </c>
       <c r="K12">
         <v>53216</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="L12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" t="s">
         <v>43</v>
       </c>
       <c r="N12" s="2">
@@ -2133,7 +2132,7 @@
       <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>38</v>
       </c>
       <c r="D13" t="s">
@@ -2145,25 +2144,25 @@
       <c r="F13">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="I13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" t="s">
         <v>40</v>
       </c>
       <c r="K13">
         <v>53216</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="3" t="s">
+      <c r="L13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" t="s">
         <v>43</v>
       </c>
       <c r="N13" s="2">
@@ -2246,7 +2245,7 @@
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>38</v>
       </c>
       <c r="D14" t="s">
@@ -2258,25 +2257,25 @@
       <c r="F14">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" t="s">
         <v>40</v>
       </c>
       <c r="K14">
         <v>53216</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="3" t="s">
+      <c r="L14" t="s">
+        <v>39</v>
+      </c>
+      <c r="M14" t="s">
         <v>43</v>
       </c>
       <c r="N14" s="2">
@@ -2359,7 +2358,7 @@
       <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" t="s">
         <v>38</v>
       </c>
       <c r="D15" t="s">
@@ -2371,25 +2370,25 @@
       <c r="F15">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="I15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" t="s">
         <v>40</v>
       </c>
       <c r="K15">
         <v>53216</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="3" t="s">
+      <c r="L15" t="s">
+        <v>39</v>
+      </c>
+      <c r="M15" t="s">
         <v>43</v>
       </c>
       <c r="N15" s="2">
@@ -2472,7 +2471,7 @@
       <c r="B16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" t="s">
         <v>38</v>
       </c>
       <c r="D16" t="s">
@@ -2484,25 +2483,25 @@
       <c r="F16">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J16" s="3" t="s">
+      <c r="I16" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" t="s">
         <v>40</v>
       </c>
       <c r="K16">
         <v>53216</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="3" t="s">
+      <c r="L16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" t="s">
         <v>43</v>
       </c>
       <c r="N16" s="2">
@@ -2585,7 +2584,7 @@
       <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" t="s">
         <v>38</v>
       </c>
       <c r="D17" t="s">
@@ -2597,25 +2596,25 @@
       <c r="F17">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" s="3" t="s">
+      <c r="I17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J17" t="s">
         <v>40</v>
       </c>
       <c r="K17">
         <v>53216</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M17" s="3" t="s">
+      <c r="L17" t="s">
+        <v>39</v>
+      </c>
+      <c r="M17" t="s">
         <v>43</v>
       </c>
       <c r="N17" s="2">
@@ -2698,7 +2697,7 @@
       <c r="B18" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>38</v>
       </c>
       <c r="D18" t="s">
@@ -2710,25 +2709,25 @@
       <c r="F18">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="I18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" t="s">
         <v>40</v>
       </c>
       <c r="K18">
         <v>53216</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M18" s="3" t="s">
+      <c r="L18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" t="s">
         <v>43</v>
       </c>
       <c r="N18" s="2">
@@ -2811,7 +2810,7 @@
       <c r="B19" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>38</v>
       </c>
       <c r="D19" t="s">
@@ -2823,25 +2822,25 @@
       <c r="F19">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="I19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" t="s">
         <v>40</v>
       </c>
       <c r="K19">
         <v>53216</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" s="3" t="s">
+      <c r="L19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M19" t="s">
         <v>43</v>
       </c>
       <c r="N19" s="2">
@@ -2924,7 +2923,7 @@
       <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" t="s">
         <v>38</v>
       </c>
       <c r="D20" t="s">
@@ -2936,25 +2935,25 @@
       <c r="F20">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="I20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" t="s">
         <v>40</v>
       </c>
       <c r="K20">
         <v>53216</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M20" s="3" t="s">
+      <c r="L20" t="s">
+        <v>39</v>
+      </c>
+      <c r="M20" t="s">
         <v>43</v>
       </c>
       <c r="N20" s="2">
@@ -3037,7 +3036,7 @@
       <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>38</v>
       </c>
       <c r="D21" t="s">
@@ -3049,25 +3048,25 @@
       <c r="F21">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="I21" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" t="s">
         <v>40</v>
       </c>
       <c r="K21">
         <v>53216</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M21" s="3" t="s">
+      <c r="L21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M21" t="s">
         <v>43</v>
       </c>
       <c r="N21" s="2">
@@ -3150,7 +3149,7 @@
       <c r="B22" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" t="s">
         <v>38</v>
       </c>
       <c r="D22" t="s">
@@ -3162,25 +3161,25 @@
       <c r="F22">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" t="s">
         <v>35</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="I22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" t="s">
         <v>40</v>
       </c>
       <c r="K22">
         <v>53216</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M22" s="3" t="s">
+      <c r="L22" t="s">
+        <v>39</v>
+      </c>
+      <c r="M22" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="2">
@@ -3263,7 +3262,7 @@
       <c r="B23" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" t="s">
         <v>38</v>
       </c>
       <c r="D23" t="s">
@@ -3275,25 +3274,25 @@
       <c r="F23">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" t="s">
         <v>35</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" s="3" t="s">
+      <c r="I23" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" t="s">
         <v>40</v>
       </c>
       <c r="K23">
         <v>53216</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M23" s="3" t="s">
+      <c r="L23" t="s">
+        <v>39</v>
+      </c>
+      <c r="M23" t="s">
         <v>43</v>
       </c>
       <c r="N23" s="2">
@@ -3376,7 +3375,7 @@
       <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" t="s">
         <v>38</v>
       </c>
       <c r="D24" t="s">
@@ -3388,25 +3387,25 @@
       <c r="F24">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="I24" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" t="s">
         <v>40</v>
       </c>
       <c r="K24">
         <v>53216</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M24" s="3" t="s">
+      <c r="L24" t="s">
+        <v>39</v>
+      </c>
+      <c r="M24" t="s">
         <v>43</v>
       </c>
       <c r="N24" s="2">
@@ -3489,7 +3488,7 @@
       <c r="B25" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" t="s">
         <v>38</v>
       </c>
       <c r="D25" t="s">
@@ -3501,25 +3500,25 @@
       <c r="F25">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="I25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" t="s">
         <v>40</v>
       </c>
       <c r="K25">
         <v>53216</v>
       </c>
-      <c r="L25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M25" s="3" t="s">
+      <c r="L25" t="s">
+        <v>39</v>
+      </c>
+      <c r="M25" t="s">
         <v>43</v>
       </c>
       <c r="N25" s="2">
@@ -3602,7 +3601,7 @@
       <c r="B26" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" t="s">
         <v>38</v>
       </c>
       <c r="D26" t="s">
@@ -3614,25 +3613,25 @@
       <c r="F26">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" t="s">
         <v>35</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" s="3" t="s">
+      <c r="I26" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" t="s">
         <v>40</v>
       </c>
       <c r="K26">
         <v>53216</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M26" s="3" t="s">
+      <c r="L26" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26" t="s">
         <v>43</v>
       </c>
       <c r="N26" s="2">
@@ -3715,7 +3714,7 @@
       <c r="B27" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" t="s">
         <v>38</v>
       </c>
       <c r="D27" t="s">
@@ -3727,25 +3726,25 @@
       <c r="F27">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="3" t="s">
+      <c r="I27" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" t="s">
         <v>40</v>
       </c>
       <c r="K27">
         <v>53216</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M27" s="3" t="s">
+      <c r="L27" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27" t="s">
         <v>43</v>
       </c>
       <c r="N27" s="2">
@@ -3828,7 +3827,7 @@
       <c r="B28" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" t="s">
         <v>38</v>
       </c>
       <c r="D28" t="s">
@@ -3840,25 +3839,25 @@
       <c r="F28">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="3" t="s">
+      <c r="I28" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" t="s">
         <v>40</v>
       </c>
       <c r="K28">
         <v>53216</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M28" s="3" t="s">
+      <c r="L28" t="s">
+        <v>39</v>
+      </c>
+      <c r="M28" t="s">
         <v>43</v>
       </c>
       <c r="N28" s="2">
@@ -3941,7 +3940,7 @@
       <c r="B29" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" t="s">
         <v>38</v>
       </c>
       <c r="D29" t="s">
@@ -3953,25 +3952,25 @@
       <c r="F29">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J29" s="3" t="s">
+      <c r="I29" t="s">
+        <v>39</v>
+      </c>
+      <c r="J29" t="s">
         <v>40</v>
       </c>
       <c r="K29">
         <v>53216</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M29" s="3" t="s">
+      <c r="L29" t="s">
+        <v>39</v>
+      </c>
+      <c r="M29" t="s">
         <v>43</v>
       </c>
       <c r="N29" s="2">
@@ -4054,7 +4053,7 @@
       <c r="B30" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" t="s">
         <v>38</v>
       </c>
       <c r="D30" t="s">
@@ -4066,25 +4065,25 @@
       <c r="F30">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" t="s">
         <v>35</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J30" s="3" t="s">
+      <c r="I30" t="s">
+        <v>39</v>
+      </c>
+      <c r="J30" t="s">
         <v>40</v>
       </c>
       <c r="K30">
         <v>53216</v>
       </c>
-      <c r="L30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M30" s="3" t="s">
+      <c r="L30" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30" t="s">
         <v>43</v>
       </c>
       <c r="N30" s="2">
@@ -4167,7 +4166,7 @@
       <c r="B31" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" t="s">
         <v>38</v>
       </c>
       <c r="D31" t="s">
@@ -4179,25 +4178,25 @@
       <c r="F31">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J31" s="3" t="s">
+      <c r="I31" t="s">
+        <v>39</v>
+      </c>
+      <c r="J31" t="s">
         <v>40</v>
       </c>
       <c r="K31">
         <v>53216</v>
       </c>
-      <c r="L31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M31" s="3" t="s">
+      <c r="L31" t="s">
+        <v>39</v>
+      </c>
+      <c r="M31" t="s">
         <v>43</v>
       </c>
       <c r="N31" s="2">
@@ -4280,7 +4279,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" t="s">
         <v>38</v>
       </c>
       <c r="D32" t="s">
@@ -4292,25 +4291,25 @@
       <c r="F32">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" t="s">
         <v>35</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J32" s="3" t="s">
+      <c r="I32" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" t="s">
         <v>40</v>
       </c>
       <c r="K32">
         <v>53216</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M32" s="3" t="s">
+      <c r="L32" t="s">
+        <v>39</v>
+      </c>
+      <c r="M32" t="s">
         <v>43</v>
       </c>
       <c r="N32" s="2">
@@ -4393,7 +4392,7 @@
       <c r="B33" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" t="s">
         <v>38</v>
       </c>
       <c r="D33" t="s">
@@ -4405,25 +4404,25 @@
       <c r="F33">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" t="s">
         <v>35</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J33" s="3" t="s">
+      <c r="I33" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" t="s">
         <v>40</v>
       </c>
       <c r="K33">
         <v>53216</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M33" s="3" t="s">
+      <c r="L33" t="s">
+        <v>39</v>
+      </c>
+      <c r="M33" t="s">
         <v>43</v>
       </c>
       <c r="N33" s="2">
@@ -4506,7 +4505,7 @@
       <c r="B34" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" t="s">
         <v>38</v>
       </c>
       <c r="D34" t="s">
@@ -4518,25 +4517,25 @@
       <c r="F34">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" t="s">
         <v>35</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34" s="3" t="s">
+      <c r="I34" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" t="s">
         <v>40</v>
       </c>
       <c r="K34">
         <v>53216</v>
       </c>
-      <c r="L34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M34" s="3" t="s">
+      <c r="L34" t="s">
+        <v>39</v>
+      </c>
+      <c r="M34" t="s">
         <v>43</v>
       </c>
       <c r="N34" s="2">
@@ -4619,7 +4618,7 @@
       <c r="B35" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" t="s">
         <v>38</v>
       </c>
       <c r="D35" t="s">
@@ -4631,25 +4630,25 @@
       <c r="F35">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J35" s="3" t="s">
+      <c r="I35" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" t="s">
         <v>40</v>
       </c>
       <c r="K35">
         <v>53216</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M35" s="3" t="s">
+      <c r="L35" t="s">
+        <v>39</v>
+      </c>
+      <c r="M35" t="s">
         <v>43</v>
       </c>
       <c r="N35" s="2">
@@ -4732,7 +4731,7 @@
       <c r="B36" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" t="s">
         <v>38</v>
       </c>
       <c r="D36" t="s">
@@ -4744,25 +4743,25 @@
       <c r="F36">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J36" s="3" t="s">
+      <c r="I36" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" t="s">
         <v>40</v>
       </c>
       <c r="K36">
         <v>53216</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M36" s="3" t="s">
+      <c r="L36" t="s">
+        <v>39</v>
+      </c>
+      <c r="M36" t="s">
         <v>43</v>
       </c>
       <c r="N36" s="2">
@@ -4845,7 +4844,7 @@
       <c r="B37" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" t="s">
         <v>38</v>
       </c>
       <c r="D37" t="s">
@@ -4857,25 +4856,25 @@
       <c r="F37">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J37" s="3" t="s">
+      <c r="I37" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" t="s">
         <v>40</v>
       </c>
       <c r="K37">
         <v>53216</v>
       </c>
-      <c r="L37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M37" s="3" t="s">
+      <c r="L37" t="s">
+        <v>39</v>
+      </c>
+      <c r="M37" t="s">
         <v>43</v>
       </c>
       <c r="N37" s="2">
@@ -4958,7 +4957,7 @@
       <c r="B38" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" t="s">
         <v>38</v>
       </c>
       <c r="D38" t="s">
@@ -4970,25 +4969,25 @@
       <c r="F38">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="3" t="s">
+      <c r="I38" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" t="s">
         <v>40</v>
       </c>
       <c r="K38">
         <v>53216</v>
       </c>
-      <c r="L38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M38" s="3" t="s">
+      <c r="L38" t="s">
+        <v>39</v>
+      </c>
+      <c r="M38" t="s">
         <v>43</v>
       </c>
       <c r="N38" s="2">
@@ -5071,7 +5070,7 @@
       <c r="B39" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" t="s">
         <v>38</v>
       </c>
       <c r="D39" t="s">
@@ -5083,25 +5082,25 @@
       <c r="F39">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" t="s">
         <v>35</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" s="3" t="s">
+      <c r="I39" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" t="s">
         <v>40</v>
       </c>
       <c r="K39">
         <v>53216</v>
       </c>
-      <c r="L39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M39" s="3" t="s">
+      <c r="L39" t="s">
+        <v>39</v>
+      </c>
+      <c r="M39" t="s">
         <v>43</v>
       </c>
       <c r="N39" s="2">
@@ -5184,7 +5183,7 @@
       <c r="B40" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" t="s">
         <v>38</v>
       </c>
       <c r="D40" t="s">
@@ -5196,25 +5195,25 @@
       <c r="F40">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" t="s">
         <v>35</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J40" s="3" t="s">
+      <c r="I40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J40" t="s">
         <v>40</v>
       </c>
       <c r="K40">
         <v>53216</v>
       </c>
-      <c r="L40" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M40" s="3" t="s">
+      <c r="L40" t="s">
+        <v>39</v>
+      </c>
+      <c r="M40" t="s">
         <v>43</v>
       </c>
       <c r="N40" s="2">
@@ -5297,7 +5296,7 @@
       <c r="B41" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" t="s">
         <v>38</v>
       </c>
       <c r="D41" t="s">
@@ -5309,25 +5308,25 @@
       <c r="F41">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" t="s">
         <v>34</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" t="s">
         <v>35</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J41" s="3" t="s">
+      <c r="I41" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" t="s">
         <v>40</v>
       </c>
       <c r="K41">
         <v>53216</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M41" s="3" t="s">
+      <c r="L41" t="s">
+        <v>39</v>
+      </c>
+      <c r="M41" t="s">
         <v>43</v>
       </c>
       <c r="N41" s="2">
@@ -5410,7 +5409,7 @@
       <c r="B42" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" t="s">
         <v>38</v>
       </c>
       <c r="D42" t="s">
@@ -5422,25 +5421,25 @@
       <c r="F42">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H42" t="s">
         <v>35</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J42" s="3" t="s">
+      <c r="I42" t="s">
+        <v>39</v>
+      </c>
+      <c r="J42" t="s">
         <v>40</v>
       </c>
       <c r="K42">
         <v>53216</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M42" s="3" t="s">
+      <c r="L42" t="s">
+        <v>39</v>
+      </c>
+      <c r="M42" t="s">
         <v>43</v>
       </c>
       <c r="N42" s="2">
@@ -5523,7 +5522,7 @@
       <c r="B43" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" t="s">
         <v>38</v>
       </c>
       <c r="D43" t="s">
@@ -5535,25 +5534,25 @@
       <c r="F43">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" t="s">
         <v>35</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J43" s="3" t="s">
+      <c r="I43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J43" t="s">
         <v>40</v>
       </c>
       <c r="K43">
         <v>53216</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M43" s="3" t="s">
+      <c r="L43" t="s">
+        <v>39</v>
+      </c>
+      <c r="M43" t="s">
         <v>43</v>
       </c>
       <c r="N43" s="2">
@@ -5636,7 +5635,7 @@
       <c r="B44" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" t="s">
         <v>38</v>
       </c>
       <c r="D44" t="s">
@@ -5648,25 +5647,25 @@
       <c r="F44">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" t="s">
         <v>35</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J44" s="3" t="s">
+      <c r="I44" t="s">
+        <v>39</v>
+      </c>
+      <c r="J44" t="s">
         <v>40</v>
       </c>
       <c r="K44">
         <v>53216</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M44" s="3" t="s">
+      <c r="L44" t="s">
+        <v>39</v>
+      </c>
+      <c r="M44" t="s">
         <v>43</v>
       </c>
       <c r="N44" s="2">
@@ -5749,7 +5748,7 @@
       <c r="B45" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" t="s">
         <v>38</v>
       </c>
       <c r="D45" t="s">
@@ -5761,25 +5760,25 @@
       <c r="F45">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" t="s">
         <v>34</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" t="s">
         <v>35</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J45" s="3" t="s">
+      <c r="I45" t="s">
+        <v>39</v>
+      </c>
+      <c r="J45" t="s">
         <v>40</v>
       </c>
       <c r="K45">
         <v>53216</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M45" s="3" t="s">
+      <c r="L45" t="s">
+        <v>39</v>
+      </c>
+      <c r="M45" t="s">
         <v>43</v>
       </c>
       <c r="N45" s="2">
@@ -5862,7 +5861,7 @@
       <c r="B46" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" t="s">
         <v>38</v>
       </c>
       <c r="D46" t="s">
@@ -5874,25 +5873,25 @@
       <c r="F46">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" t="s">
         <v>35</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J46" s="3" t="s">
+      <c r="I46" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" t="s">
         <v>40</v>
       </c>
       <c r="K46">
         <v>53216</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M46" s="3" t="s">
+      <c r="L46" t="s">
+        <v>39</v>
+      </c>
+      <c r="M46" t="s">
         <v>43</v>
       </c>
       <c r="N46" s="2">
@@ -5975,7 +5974,7 @@
       <c r="B47" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" t="s">
         <v>38</v>
       </c>
       <c r="D47" t="s">
@@ -5987,25 +5986,25 @@
       <c r="F47">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" t="s">
         <v>35</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J47" s="3" t="s">
+      <c r="I47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J47" t="s">
         <v>40</v>
       </c>
       <c r="K47">
         <v>53216</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M47" s="3" t="s">
+      <c r="L47" t="s">
+        <v>39</v>
+      </c>
+      <c r="M47" t="s">
         <v>43</v>
       </c>
       <c r="N47" s="2">
@@ -6088,7 +6087,7 @@
       <c r="B48" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" t="s">
         <v>38</v>
       </c>
       <c r="D48" t="s">
@@ -6100,25 +6099,25 @@
       <c r="F48">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H48" t="s">
         <v>35</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J48" s="3" t="s">
+      <c r="I48" t="s">
+        <v>39</v>
+      </c>
+      <c r="J48" t="s">
         <v>40</v>
       </c>
       <c r="K48">
         <v>53216</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M48" s="3" t="s">
+      <c r="L48" t="s">
+        <v>39</v>
+      </c>
+      <c r="M48" t="s">
         <v>43</v>
       </c>
       <c r="N48" s="2">
@@ -6201,7 +6200,7 @@
       <c r="B49" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" t="s">
         <v>38</v>
       </c>
       <c r="D49" t="s">
@@ -6213,25 +6212,25 @@
       <c r="F49">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" t="s">
         <v>35</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J49" s="3" t="s">
+      <c r="I49" t="s">
+        <v>39</v>
+      </c>
+      <c r="J49" t="s">
         <v>40</v>
       </c>
       <c r="K49">
         <v>53216</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M49" s="3" t="s">
+      <c r="L49" t="s">
+        <v>39</v>
+      </c>
+      <c r="M49" t="s">
         <v>43</v>
       </c>
       <c r="N49" s="2">
@@ -6314,7 +6313,7 @@
       <c r="B50" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" t="s">
         <v>38</v>
       </c>
       <c r="D50" t="s">
@@ -6326,25 +6325,25 @@
       <c r="F50">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H50" t="s">
         <v>35</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J50" s="3" t="s">
+      <c r="I50" t="s">
+        <v>39</v>
+      </c>
+      <c r="J50" t="s">
         <v>40</v>
       </c>
       <c r="K50">
         <v>53216</v>
       </c>
-      <c r="L50" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M50" s="3" t="s">
+      <c r="L50" t="s">
+        <v>39</v>
+      </c>
+      <c r="M50" t="s">
         <v>43</v>
       </c>
       <c r="N50" s="2">
@@ -6427,7 +6426,7 @@
       <c r="B51" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" t="s">
         <v>38</v>
       </c>
       <c r="D51" t="s">
@@ -6439,25 +6438,25 @@
       <c r="F51">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" t="s">
         <v>34</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H51" t="s">
         <v>35</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J51" s="3" t="s">
+      <c r="I51" t="s">
+        <v>39</v>
+      </c>
+      <c r="J51" t="s">
         <v>40</v>
       </c>
       <c r="K51">
         <v>53216</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M51" s="3" t="s">
+      <c r="L51" t="s">
+        <v>39</v>
+      </c>
+      <c r="M51" t="s">
         <v>43</v>
       </c>
       <c r="N51" s="2">
@@ -6540,7 +6539,7 @@
       <c r="B52" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" t="s">
         <v>38</v>
       </c>
       <c r="D52" t="s">
@@ -6552,25 +6551,25 @@
       <c r="F52">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H52" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J52" s="3" t="s">
+      <c r="I52" t="s">
+        <v>39</v>
+      </c>
+      <c r="J52" t="s">
         <v>40</v>
       </c>
       <c r="K52">
         <v>53216</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M52" s="3" t="s">
+      <c r="L52" t="s">
+        <v>39</v>
+      </c>
+      <c r="M52" t="s">
         <v>43</v>
       </c>
       <c r="N52" s="2">
@@ -6653,7 +6652,7 @@
       <c r="B53" t="s">
         <v>37</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" t="s">
         <v>38</v>
       </c>
       <c r="D53" t="s">
@@ -6665,25 +6664,25 @@
       <c r="F53">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" t="s">
         <v>35</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J53" s="3" t="s">
+      <c r="I53" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" t="s">
         <v>40</v>
       </c>
       <c r="K53">
         <v>53216</v>
       </c>
-      <c r="L53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M53" s="3" t="s">
+      <c r="L53" t="s">
+        <v>39</v>
+      </c>
+      <c r="M53" t="s">
         <v>43</v>
       </c>
       <c r="N53" s="2">
@@ -6766,7 +6765,7 @@
       <c r="B54" t="s">
         <v>37</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" t="s">
         <v>38</v>
       </c>
       <c r="D54" t="s">
@@ -6778,25 +6777,25 @@
       <c r="F54">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" t="s">
         <v>34</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H54" t="s">
         <v>35</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J54" s="3" t="s">
+      <c r="I54" t="s">
+        <v>39</v>
+      </c>
+      <c r="J54" t="s">
         <v>40</v>
       </c>
       <c r="K54">
         <v>53216</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M54" s="3" t="s">
+      <c r="L54" t="s">
+        <v>39</v>
+      </c>
+      <c r="M54" t="s">
         <v>43</v>
       </c>
       <c r="N54" s="2">
@@ -6879,7 +6878,7 @@
       <c r="B55" t="s">
         <v>37</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" t="s">
         <v>38</v>
       </c>
       <c r="D55" t="s">
@@ -6891,25 +6890,25 @@
       <c r="F55">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" t="s">
         <v>35</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J55" s="3" t="s">
+      <c r="I55" t="s">
+        <v>39</v>
+      </c>
+      <c r="J55" t="s">
         <v>40</v>
       </c>
       <c r="K55">
         <v>53216</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M55" s="3" t="s">
+      <c r="L55" t="s">
+        <v>39</v>
+      </c>
+      <c r="M55" t="s">
         <v>43</v>
       </c>
       <c r="N55" s="2">
@@ -6992,7 +6991,7 @@
       <c r="B56" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" t="s">
         <v>38</v>
       </c>
       <c r="D56" t="s">
@@ -7004,25 +7003,25 @@
       <c r="F56">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" t="s">
         <v>34</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H56" t="s">
         <v>35</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J56" s="3" t="s">
+      <c r="I56" t="s">
+        <v>39</v>
+      </c>
+      <c r="J56" t="s">
         <v>40</v>
       </c>
       <c r="K56">
         <v>53216</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M56" s="3" t="s">
+      <c r="L56" t="s">
+        <v>39</v>
+      </c>
+      <c r="M56" t="s">
         <v>43</v>
       </c>
       <c r="N56" s="2">
@@ -7105,7 +7104,7 @@
       <c r="B57" t="s">
         <v>37</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" t="s">
         <v>38</v>
       </c>
       <c r="D57" t="s">
@@ -7117,25 +7116,25 @@
       <c r="F57">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" t="s">
         <v>34</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H57" t="s">
         <v>35</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J57" s="3" t="s">
+      <c r="I57" t="s">
+        <v>39</v>
+      </c>
+      <c r="J57" t="s">
         <v>40</v>
       </c>
       <c r="K57">
         <v>53216</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M57" s="3" t="s">
+      <c r="L57" t="s">
+        <v>39</v>
+      </c>
+      <c r="M57" t="s">
         <v>43</v>
       </c>
       <c r="N57" s="2">
@@ -7218,7 +7217,7 @@
       <c r="B58" t="s">
         <v>37</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" t="s">
         <v>38</v>
       </c>
       <c r="D58" t="s">
@@ -7230,25 +7229,25 @@
       <c r="F58">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" t="s">
         <v>34</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H58" t="s">
         <v>35</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J58" s="3" t="s">
+      <c r="I58" t="s">
+        <v>39</v>
+      </c>
+      <c r="J58" t="s">
         <v>40</v>
       </c>
       <c r="K58">
         <v>53216</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M58" s="3" t="s">
+      <c r="L58" t="s">
+        <v>39</v>
+      </c>
+      <c r="M58" t="s">
         <v>43</v>
       </c>
       <c r="N58" s="2">
@@ -7331,7 +7330,7 @@
       <c r="B59" t="s">
         <v>37</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" t="s">
         <v>38</v>
       </c>
       <c r="D59" t="s">
@@ -7343,25 +7342,25 @@
       <c r="F59">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" t="s">
         <v>34</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H59" t="s">
         <v>35</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J59" s="3" t="s">
+      <c r="I59" t="s">
+        <v>39</v>
+      </c>
+      <c r="J59" t="s">
         <v>40</v>
       </c>
       <c r="K59">
         <v>53216</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M59" s="3" t="s">
+      <c r="L59" t="s">
+        <v>39</v>
+      </c>
+      <c r="M59" t="s">
         <v>43</v>
       </c>
       <c r="N59" s="2">
@@ -7444,7 +7443,7 @@
       <c r="B60" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" t="s">
         <v>38</v>
       </c>
       <c r="D60" t="s">
@@ -7456,25 +7455,25 @@
       <c r="F60">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" t="s">
         <v>34</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H60" t="s">
         <v>35</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J60" s="3" t="s">
+      <c r="I60" t="s">
+        <v>39</v>
+      </c>
+      <c r="J60" t="s">
         <v>40</v>
       </c>
       <c r="K60">
         <v>53216</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M60" s="3" t="s">
+      <c r="L60" t="s">
+        <v>39</v>
+      </c>
+      <c r="M60" t="s">
         <v>43</v>
       </c>
       <c r="N60" s="2">
@@ -7557,7 +7556,7 @@
       <c r="B61" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" t="s">
         <v>38</v>
       </c>
       <c r="D61" t="s">
@@ -7569,25 +7568,25 @@
       <c r="F61">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" t="s">
         <v>34</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H61" t="s">
         <v>35</v>
       </c>
-      <c r="I61" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J61" s="3" t="s">
+      <c r="I61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J61" t="s">
         <v>40</v>
       </c>
       <c r="K61">
         <v>53216</v>
       </c>
-      <c r="L61" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M61" s="3" t="s">
+      <c r="L61" t="s">
+        <v>39</v>
+      </c>
+      <c r="M61" t="s">
         <v>43</v>
       </c>
       <c r="N61" s="2">
@@ -7670,7 +7669,7 @@
       <c r="B62" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" t="s">
         <v>38</v>
       </c>
       <c r="D62" t="s">
@@ -7682,25 +7681,25 @@
       <c r="F62">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" t="s">
         <v>34</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" t="s">
         <v>35</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J62" s="3" t="s">
+      <c r="I62" t="s">
+        <v>39</v>
+      </c>
+      <c r="J62" t="s">
         <v>40</v>
       </c>
       <c r="K62">
         <v>53216</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M62" s="3" t="s">
+      <c r="L62" t="s">
+        <v>39</v>
+      </c>
+      <c r="M62" t="s">
         <v>43</v>
       </c>
       <c r="N62" s="2">
@@ -7783,7 +7782,7 @@
       <c r="B63" t="s">
         <v>37</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" t="s">
         <v>38</v>
       </c>
       <c r="D63" t="s">
@@ -7795,25 +7794,25 @@
       <c r="F63">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" t="s">
         <v>34</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H63" t="s">
         <v>35</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J63" s="3" t="s">
+      <c r="I63" t="s">
+        <v>39</v>
+      </c>
+      <c r="J63" t="s">
         <v>40</v>
       </c>
       <c r="K63">
         <v>53216</v>
       </c>
-      <c r="L63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M63" s="3" t="s">
+      <c r="L63" t="s">
+        <v>39</v>
+      </c>
+      <c r="M63" t="s">
         <v>43</v>
       </c>
       <c r="N63" s="2">
@@ -7896,7 +7895,7 @@
       <c r="B64" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" t="s">
         <v>38</v>
       </c>
       <c r="D64" t="s">
@@ -7908,25 +7907,25 @@
       <c r="F64">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" t="s">
         <v>34</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H64" t="s">
         <v>35</v>
       </c>
-      <c r="I64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J64" s="3" t="s">
+      <c r="I64" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" t="s">
         <v>40</v>
       </c>
       <c r="K64">
         <v>53216</v>
       </c>
-      <c r="L64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M64" s="3" t="s">
+      <c r="L64" t="s">
+        <v>39</v>
+      </c>
+      <c r="M64" t="s">
         <v>43</v>
       </c>
       <c r="N64" s="2">
@@ -8009,7 +8008,7 @@
       <c r="B65" t="s">
         <v>37</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" t="s">
         <v>38</v>
       </c>
       <c r="D65" t="s">
@@ -8021,25 +8020,25 @@
       <c r="F65">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" t="s">
         <v>34</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H65" t="s">
         <v>35</v>
       </c>
-      <c r="I65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J65" s="3" t="s">
+      <c r="I65" t="s">
+        <v>39</v>
+      </c>
+      <c r="J65" t="s">
         <v>40</v>
       </c>
       <c r="K65">
         <v>53216</v>
       </c>
-      <c r="L65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M65" s="3" t="s">
+      <c r="L65" t="s">
+        <v>39</v>
+      </c>
+      <c r="M65" t="s">
         <v>43</v>
       </c>
       <c r="N65" s="2">
@@ -8122,7 +8121,7 @@
       <c r="B66" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" t="s">
         <v>38</v>
       </c>
       <c r="D66" t="s">
@@ -8134,25 +8133,25 @@
       <c r="F66">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" t="s">
         <v>34</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H66" t="s">
         <v>35</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J66" s="3" t="s">
+      <c r="I66" t="s">
+        <v>39</v>
+      </c>
+      <c r="J66" t="s">
         <v>40</v>
       </c>
       <c r="K66">
         <v>53216</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M66" s="3" t="s">
+      <c r="L66" t="s">
+        <v>39</v>
+      </c>
+      <c r="M66" t="s">
         <v>43</v>
       </c>
       <c r="N66" s="2">
@@ -8235,7 +8234,7 @@
       <c r="B67" t="s">
         <v>37</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" t="s">
         <v>38</v>
       </c>
       <c r="D67" t="s">
@@ -8247,25 +8246,25 @@
       <c r="F67">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" t="s">
         <v>34</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H67" t="s">
         <v>35</v>
       </c>
-      <c r="I67" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J67" s="3" t="s">
+      <c r="I67" t="s">
+        <v>39</v>
+      </c>
+      <c r="J67" t="s">
         <v>40</v>
       </c>
       <c r="K67">
         <v>53216</v>
       </c>
-      <c r="L67" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M67" s="3" t="s">
+      <c r="L67" t="s">
+        <v>39</v>
+      </c>
+      <c r="M67" t="s">
         <v>43</v>
       </c>
       <c r="N67" s="2">
@@ -8348,7 +8347,7 @@
       <c r="B68" t="s">
         <v>37</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" t="s">
         <v>38</v>
       </c>
       <c r="D68" t="s">
@@ -8360,25 +8359,25 @@
       <c r="F68">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" t="s">
         <v>34</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H68" t="s">
         <v>35</v>
       </c>
-      <c r="I68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J68" s="3" t="s">
+      <c r="I68" t="s">
+        <v>39</v>
+      </c>
+      <c r="J68" t="s">
         <v>40</v>
       </c>
       <c r="K68">
         <v>53216</v>
       </c>
-      <c r="L68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M68" s="3" t="s">
+      <c r="L68" t="s">
+        <v>39</v>
+      </c>
+      <c r="M68" t="s">
         <v>43</v>
       </c>
       <c r="N68" s="2">
@@ -8461,7 +8460,7 @@
       <c r="B69" t="s">
         <v>37</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" t="s">
         <v>38</v>
       </c>
       <c r="D69" t="s">
@@ -8473,25 +8472,25 @@
       <c r="F69">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" t="s">
         <v>34</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H69" t="s">
         <v>35</v>
       </c>
-      <c r="I69" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J69" s="3" t="s">
+      <c r="I69" t="s">
+        <v>39</v>
+      </c>
+      <c r="J69" t="s">
         <v>40</v>
       </c>
       <c r="K69">
         <v>53216</v>
       </c>
-      <c r="L69" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M69" s="3" t="s">
+      <c r="L69" t="s">
+        <v>39</v>
+      </c>
+      <c r="M69" t="s">
         <v>43</v>
       </c>
       <c r="N69" s="2">
@@ -8574,7 +8573,7 @@
       <c r="B70" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" t="s">
         <v>38</v>
       </c>
       <c r="D70" t="s">
@@ -8586,25 +8585,25 @@
       <c r="F70">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" t="s">
         <v>34</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H70" t="s">
         <v>35</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J70" s="3" t="s">
+      <c r="I70" t="s">
+        <v>39</v>
+      </c>
+      <c r="J70" t="s">
         <v>40</v>
       </c>
       <c r="K70">
         <v>53216</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M70" s="3" t="s">
+      <c r="L70" t="s">
+        <v>39</v>
+      </c>
+      <c r="M70" t="s">
         <v>43</v>
       </c>
       <c r="N70" s="2">
@@ -8687,7 +8686,7 @@
       <c r="B71" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" t="s">
         <v>38</v>
       </c>
       <c r="D71" t="s">
@@ -8699,25 +8698,25 @@
       <c r="F71">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" t="s">
         <v>34</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H71" t="s">
         <v>35</v>
       </c>
-      <c r="I71" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J71" s="3" t="s">
+      <c r="I71" t="s">
+        <v>39</v>
+      </c>
+      <c r="J71" t="s">
         <v>40</v>
       </c>
       <c r="K71">
         <v>53216</v>
       </c>
-      <c r="L71" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M71" s="3" t="s">
+      <c r="L71" t="s">
+        <v>39</v>
+      </c>
+      <c r="M71" t="s">
         <v>43</v>
       </c>
       <c r="N71" s="2">
@@ -8800,7 +8799,7 @@
       <c r="B72" t="s">
         <v>37</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" t="s">
         <v>38</v>
       </c>
       <c r="D72" t="s">
@@ -8812,25 +8811,25 @@
       <c r="F72">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" t="s">
         <v>34</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" t="s">
         <v>35</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J72" s="3" t="s">
+      <c r="I72" t="s">
+        <v>39</v>
+      </c>
+      <c r="J72" t="s">
         <v>40</v>
       </c>
       <c r="K72">
         <v>53216</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M72" s="3" t="s">
+      <c r="L72" t="s">
+        <v>39</v>
+      </c>
+      <c r="M72" t="s">
         <v>43</v>
       </c>
       <c r="N72" s="2">
@@ -8913,7 +8912,7 @@
       <c r="B73" t="s">
         <v>37</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" t="s">
         <v>38</v>
       </c>
       <c r="D73" t="s">
@@ -8925,25 +8924,25 @@
       <c r="F73">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" t="s">
         <v>34</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="H73" t="s">
         <v>35</v>
       </c>
-      <c r="I73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J73" s="3" t="s">
+      <c r="I73" t="s">
+        <v>39</v>
+      </c>
+      <c r="J73" t="s">
         <v>40</v>
       </c>
       <c r="K73">
         <v>53216</v>
       </c>
-      <c r="L73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M73" s="3" t="s">
+      <c r="L73" t="s">
+        <v>39</v>
+      </c>
+      <c r="M73" t="s">
         <v>43</v>
       </c>
       <c r="N73" s="2">
@@ -9026,7 +9025,7 @@
       <c r="B74" t="s">
         <v>37</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" t="s">
         <v>38</v>
       </c>
       <c r="D74" t="s">
@@ -9038,25 +9037,25 @@
       <c r="F74">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" t="s">
         <v>34</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="H74" t="s">
         <v>35</v>
       </c>
-      <c r="I74" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J74" s="3" t="s">
+      <c r="I74" t="s">
+        <v>39</v>
+      </c>
+      <c r="J74" t="s">
         <v>40</v>
       </c>
       <c r="K74">
         <v>53216</v>
       </c>
-      <c r="L74" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M74" s="3" t="s">
+      <c r="L74" t="s">
+        <v>39</v>
+      </c>
+      <c r="M74" t="s">
         <v>43</v>
       </c>
       <c r="N74" s="2">
@@ -9139,7 +9138,7 @@
       <c r="B75" t="s">
         <v>37</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" t="s">
         <v>38</v>
       </c>
       <c r="D75" t="s">
@@ -9151,25 +9150,25 @@
       <c r="F75">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" t="s">
         <v>34</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="H75" t="s">
         <v>35</v>
       </c>
-      <c r="I75" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J75" s="3" t="s">
+      <c r="I75" t="s">
+        <v>39</v>
+      </c>
+      <c r="J75" t="s">
         <v>40</v>
       </c>
       <c r="K75">
         <v>53216</v>
       </c>
-      <c r="L75" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M75" s="3" t="s">
+      <c r="L75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M75" t="s">
         <v>43</v>
       </c>
       <c r="N75" s="2">
@@ -9252,7 +9251,7 @@
       <c r="B76" t="s">
         <v>37</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" t="s">
         <v>38</v>
       </c>
       <c r="D76" t="s">
@@ -9264,25 +9263,25 @@
       <c r="F76">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" t="s">
         <v>34</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" t="s">
         <v>35</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J76" s="3" t="s">
+      <c r="I76" t="s">
+        <v>39</v>
+      </c>
+      <c r="J76" t="s">
         <v>40</v>
       </c>
       <c r="K76">
         <v>53216</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M76" s="3" t="s">
+      <c r="L76" t="s">
+        <v>39</v>
+      </c>
+      <c r="M76" t="s">
         <v>43</v>
       </c>
       <c r="N76" s="2">
@@ -9365,7 +9364,7 @@
       <c r="B77" t="s">
         <v>37</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" t="s">
         <v>38</v>
       </c>
       <c r="D77" t="s">
@@ -9377,25 +9376,25 @@
       <c r="F77">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" t="s">
         <v>34</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="H77" t="s">
         <v>35</v>
       </c>
-      <c r="I77" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J77" s="3" t="s">
+      <c r="I77" t="s">
+        <v>39</v>
+      </c>
+      <c r="J77" t="s">
         <v>40</v>
       </c>
       <c r="K77">
         <v>53216</v>
       </c>
-      <c r="L77" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M77" s="3" t="s">
+      <c r="L77" t="s">
+        <v>39</v>
+      </c>
+      <c r="M77" t="s">
         <v>43</v>
       </c>
       <c r="N77" s="2">
@@ -9478,7 +9477,7 @@
       <c r="B78" t="s">
         <v>37</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" t="s">
         <v>38</v>
       </c>
       <c r="D78" t="s">
@@ -9490,25 +9489,25 @@
       <c r="F78">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" t="s">
         <v>34</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" t="s">
         <v>35</v>
       </c>
-      <c r="I78" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J78" s="3" t="s">
+      <c r="I78" t="s">
+        <v>39</v>
+      </c>
+      <c r="J78" t="s">
         <v>40</v>
       </c>
       <c r="K78">
         <v>53216</v>
       </c>
-      <c r="L78" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M78" s="3" t="s">
+      <c r="L78" t="s">
+        <v>39</v>
+      </c>
+      <c r="M78" t="s">
         <v>43</v>
       </c>
       <c r="N78" s="2">
@@ -9591,7 +9590,7 @@
       <c r="B79" t="s">
         <v>37</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" t="s">
         <v>38</v>
       </c>
       <c r="D79" t="s">
@@ -9603,25 +9602,25 @@
       <c r="F79">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" t="s">
         <v>34</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="H79" t="s">
         <v>35</v>
       </c>
-      <c r="I79" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J79" s="3" t="s">
+      <c r="I79" t="s">
+        <v>39</v>
+      </c>
+      <c r="J79" t="s">
         <v>40</v>
       </c>
       <c r="K79">
         <v>53216</v>
       </c>
-      <c r="L79" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M79" s="3" t="s">
+      <c r="L79" t="s">
+        <v>39</v>
+      </c>
+      <c r="M79" t="s">
         <v>43</v>
       </c>
       <c r="N79" s="2">
@@ -9704,7 +9703,7 @@
       <c r="B80" t="s">
         <v>37</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" t="s">
         <v>38</v>
       </c>
       <c r="D80" t="s">
@@ -9716,25 +9715,25 @@
       <c r="F80">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" t="s">
         <v>34</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="H80" t="s">
         <v>35</v>
       </c>
-      <c r="I80" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J80" s="3" t="s">
+      <c r="I80" t="s">
+        <v>39</v>
+      </c>
+      <c r="J80" t="s">
         <v>40</v>
       </c>
       <c r="K80">
         <v>53216</v>
       </c>
-      <c r="L80" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M80" s="3" t="s">
+      <c r="L80" t="s">
+        <v>39</v>
+      </c>
+      <c r="M80" t="s">
         <v>43</v>
       </c>
       <c r="N80" s="2">
@@ -9817,7 +9816,7 @@
       <c r="B81" t="s">
         <v>37</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" t="s">
         <v>38</v>
       </c>
       <c r="D81" t="s">
@@ -9829,25 +9828,25 @@
       <c r="F81">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" t="s">
         <v>34</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H81" t="s">
         <v>35</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J81" s="3" t="s">
+      <c r="I81" t="s">
+        <v>39</v>
+      </c>
+      <c r="J81" t="s">
         <v>40</v>
       </c>
       <c r="K81">
         <v>53216</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M81" s="3" t="s">
+      <c r="L81" t="s">
+        <v>39</v>
+      </c>
+      <c r="M81" t="s">
         <v>43</v>
       </c>
       <c r="N81" s="2">
@@ -9930,7 +9929,7 @@
       <c r="B82" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" t="s">
         <v>38</v>
       </c>
       <c r="D82" t="s">
@@ -9942,25 +9941,25 @@
       <c r="F82">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G82" t="s">
         <v>34</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="H82" t="s">
         <v>35</v>
       </c>
-      <c r="I82" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J82" s="3" t="s">
+      <c r="I82" t="s">
+        <v>39</v>
+      </c>
+      <c r="J82" t="s">
         <v>40</v>
       </c>
       <c r="K82">
         <v>53216</v>
       </c>
-      <c r="L82" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M82" s="3" t="s">
+      <c r="L82" t="s">
+        <v>39</v>
+      </c>
+      <c r="M82" t="s">
         <v>43</v>
       </c>
       <c r="N82" s="2">
@@ -10043,7 +10042,7 @@
       <c r="B83" t="s">
         <v>37</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" t="s">
         <v>38</v>
       </c>
       <c r="D83" t="s">
@@ -10055,25 +10054,25 @@
       <c r="F83">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="G83" t="s">
         <v>34</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="H83" t="s">
         <v>35</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J83" s="3" t="s">
+      <c r="I83" t="s">
+        <v>39</v>
+      </c>
+      <c r="J83" t="s">
         <v>40</v>
       </c>
       <c r="K83">
         <v>53216</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M83" s="3" t="s">
+      <c r="L83" t="s">
+        <v>39</v>
+      </c>
+      <c r="M83" t="s">
         <v>43</v>
       </c>
       <c r="N83" s="2">
@@ -10156,7 +10155,7 @@
       <c r="B84" t="s">
         <v>37</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" t="s">
         <v>38</v>
       </c>
       <c r="D84" t="s">
@@ -10168,25 +10167,25 @@
       <c r="F84">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" t="s">
         <v>34</v>
       </c>
-      <c r="H84" s="3" t="s">
+      <c r="H84" t="s">
         <v>35</v>
       </c>
-      <c r="I84" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J84" s="3" t="s">
+      <c r="I84" t="s">
+        <v>39</v>
+      </c>
+      <c r="J84" t="s">
         <v>40</v>
       </c>
       <c r="K84">
         <v>53216</v>
       </c>
-      <c r="L84" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M84" s="3" t="s">
+      <c r="L84" t="s">
+        <v>39</v>
+      </c>
+      <c r="M84" t="s">
         <v>43</v>
       </c>
       <c r="N84" s="2">
@@ -10269,7 +10268,7 @@
       <c r="B85" t="s">
         <v>37</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" t="s">
         <v>38</v>
       </c>
       <c r="D85" t="s">
@@ -10281,25 +10280,25 @@
       <c r="F85">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" t="s">
         <v>34</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="H85" t="s">
         <v>35</v>
       </c>
-      <c r="I85" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J85" s="3" t="s">
+      <c r="I85" t="s">
+        <v>39</v>
+      </c>
+      <c r="J85" t="s">
         <v>40</v>
       </c>
       <c r="K85">
         <v>53216</v>
       </c>
-      <c r="L85" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M85" s="3" t="s">
+      <c r="L85" t="s">
+        <v>39</v>
+      </c>
+      <c r="M85" t="s">
         <v>43</v>
       </c>
       <c r="N85" s="2">
@@ -10382,7 +10381,7 @@
       <c r="B86" t="s">
         <v>37</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" t="s">
         <v>38</v>
       </c>
       <c r="D86" t="s">
@@ -10394,25 +10393,25 @@
       <c r="F86">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" t="s">
         <v>34</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="H86" t="s">
         <v>35</v>
       </c>
-      <c r="I86" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J86" s="3" t="s">
+      <c r="I86" t="s">
+        <v>39</v>
+      </c>
+      <c r="J86" t="s">
         <v>40</v>
       </c>
       <c r="K86">
         <v>53216</v>
       </c>
-      <c r="L86" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M86" s="3" t="s">
+      <c r="L86" t="s">
+        <v>39</v>
+      </c>
+      <c r="M86" t="s">
         <v>43</v>
       </c>
       <c r="N86" s="2">
@@ -10495,7 +10494,7 @@
       <c r="B87" t="s">
         <v>37</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" t="s">
         <v>38</v>
       </c>
       <c r="D87" t="s">
@@ -10507,25 +10506,25 @@
       <c r="F87">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="G87" t="s">
         <v>34</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="H87" t="s">
         <v>35</v>
       </c>
-      <c r="I87" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J87" s="3" t="s">
+      <c r="I87" t="s">
+        <v>39</v>
+      </c>
+      <c r="J87" t="s">
         <v>40</v>
       </c>
       <c r="K87">
         <v>53216</v>
       </c>
-      <c r="L87" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M87" s="3" t="s">
+      <c r="L87" t="s">
+        <v>39</v>
+      </c>
+      <c r="M87" t="s">
         <v>43</v>
       </c>
       <c r="N87" s="2">
@@ -10608,7 +10607,7 @@
       <c r="B88" t="s">
         <v>37</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" t="s">
         <v>38</v>
       </c>
       <c r="D88" t="s">
@@ -10620,25 +10619,25 @@
       <c r="F88">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" t="s">
         <v>34</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="H88" t="s">
         <v>35</v>
       </c>
-      <c r="I88" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J88" s="3" t="s">
+      <c r="I88" t="s">
+        <v>39</v>
+      </c>
+      <c r="J88" t="s">
         <v>40</v>
       </c>
       <c r="K88">
         <v>53216</v>
       </c>
-      <c r="L88" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M88" s="3" t="s">
+      <c r="L88" t="s">
+        <v>39</v>
+      </c>
+      <c r="M88" t="s">
         <v>43</v>
       </c>
       <c r="N88" s="2">
@@ -10721,7 +10720,7 @@
       <c r="B89" t="s">
         <v>37</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" t="s">
         <v>38</v>
       </c>
       <c r="D89" t="s">
@@ -10733,25 +10732,25 @@
       <c r="F89">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" t="s">
         <v>34</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="H89" t="s">
         <v>35</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J89" s="3" t="s">
+      <c r="I89" t="s">
+        <v>39</v>
+      </c>
+      <c r="J89" t="s">
         <v>40</v>
       </c>
       <c r="K89">
         <v>53216</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M89" s="3" t="s">
+      <c r="L89" t="s">
+        <v>39</v>
+      </c>
+      <c r="M89" t="s">
         <v>43</v>
       </c>
       <c r="N89" s="2">
@@ -10834,7 +10833,7 @@
       <c r="B90" t="s">
         <v>37</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" t="s">
         <v>38</v>
       </c>
       <c r="D90" t="s">
@@ -10846,25 +10845,25 @@
       <c r="F90">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G90" t="s">
         <v>34</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="H90" t="s">
         <v>35</v>
       </c>
-      <c r="I90" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J90" s="3" t="s">
+      <c r="I90" t="s">
+        <v>39</v>
+      </c>
+      <c r="J90" t="s">
         <v>40</v>
       </c>
       <c r="K90">
         <v>53216</v>
       </c>
-      <c r="L90" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M90" s="3" t="s">
+      <c r="L90" t="s">
+        <v>39</v>
+      </c>
+      <c r="M90" t="s">
         <v>43</v>
       </c>
       <c r="N90" s="2">
@@ -10947,7 +10946,7 @@
       <c r="B91" t="s">
         <v>37</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" t="s">
         <v>38</v>
       </c>
       <c r="D91" t="s">
@@ -10959,25 +10958,25 @@
       <c r="F91">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" t="s">
         <v>34</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="H91" t="s">
         <v>35</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J91" s="3" t="s">
+      <c r="I91" t="s">
+        <v>39</v>
+      </c>
+      <c r="J91" t="s">
         <v>40</v>
       </c>
       <c r="K91">
         <v>53216</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M91" s="3" t="s">
+      <c r="L91" t="s">
+        <v>39</v>
+      </c>
+      <c r="M91" t="s">
         <v>43</v>
       </c>
       <c r="N91" s="2">
@@ -11060,7 +11059,7 @@
       <c r="B92" t="s">
         <v>37</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" t="s">
         <v>38</v>
       </c>
       <c r="D92" t="s">
@@ -11072,25 +11071,25 @@
       <c r="F92">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" t="s">
         <v>34</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="H92" t="s">
         <v>35</v>
       </c>
-      <c r="I92" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J92" s="3" t="s">
+      <c r="I92" t="s">
+        <v>39</v>
+      </c>
+      <c r="J92" t="s">
         <v>40</v>
       </c>
       <c r="K92">
         <v>53216</v>
       </c>
-      <c r="L92" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M92" s="3" t="s">
+      <c r="L92" t="s">
+        <v>39</v>
+      </c>
+      <c r="M92" t="s">
         <v>43</v>
       </c>
       <c r="N92" s="2">
@@ -11173,7 +11172,7 @@
       <c r="B93" t="s">
         <v>37</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" t="s">
         <v>38</v>
       </c>
       <c r="D93" t="s">
@@ -11185,25 +11184,25 @@
       <c r="F93">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="G93" t="s">
         <v>34</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H93" t="s">
         <v>35</v>
       </c>
-      <c r="I93" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J93" s="3" t="s">
+      <c r="I93" t="s">
+        <v>39</v>
+      </c>
+      <c r="J93" t="s">
         <v>40</v>
       </c>
       <c r="K93">
         <v>53216</v>
       </c>
-      <c r="L93" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M93" s="3" t="s">
+      <c r="L93" t="s">
+        <v>39</v>
+      </c>
+      <c r="M93" t="s">
         <v>43</v>
       </c>
       <c r="N93" s="2">
@@ -11286,7 +11285,7 @@
       <c r="B94" t="s">
         <v>37</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" t="s">
         <v>38</v>
       </c>
       <c r="D94" t="s">
@@ -11298,25 +11297,25 @@
       <c r="F94">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" t="s">
         <v>34</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H94" t="s">
         <v>35</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J94" s="3" t="s">
+      <c r="I94" t="s">
+        <v>39</v>
+      </c>
+      <c r="J94" t="s">
         <v>40</v>
       </c>
       <c r="K94">
         <v>53216</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M94" s="3" t="s">
+      <c r="L94" t="s">
+        <v>39</v>
+      </c>
+      <c r="M94" t="s">
         <v>43</v>
       </c>
       <c r="N94" s="2">
@@ -11399,7 +11398,7 @@
       <c r="B95" t="s">
         <v>37</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" t="s">
         <v>38</v>
       </c>
       <c r="D95" t="s">
@@ -11411,25 +11410,25 @@
       <c r="F95">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" t="s">
         <v>34</v>
       </c>
-      <c r="H95" s="3" t="s">
+      <c r="H95" t="s">
         <v>35</v>
       </c>
-      <c r="I95" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J95" s="3" t="s">
+      <c r="I95" t="s">
+        <v>39</v>
+      </c>
+      <c r="J95" t="s">
         <v>40</v>
       </c>
       <c r="K95">
         <v>53216</v>
       </c>
-      <c r="L95" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M95" s="3" t="s">
+      <c r="L95" t="s">
+        <v>39</v>
+      </c>
+      <c r="M95" t="s">
         <v>43</v>
       </c>
       <c r="N95" s="2">
@@ -11512,7 +11511,7 @@
       <c r="B96" t="s">
         <v>37</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" t="s">
         <v>38</v>
       </c>
       <c r="D96" t="s">
@@ -11524,25 +11523,25 @@
       <c r="F96">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="G96" t="s">
         <v>34</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="H96" t="s">
         <v>35</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J96" s="3" t="s">
+      <c r="I96" t="s">
+        <v>39</v>
+      </c>
+      <c r="J96" t="s">
         <v>40</v>
       </c>
       <c r="K96">
         <v>53216</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M96" s="3" t="s">
+      <c r="L96" t="s">
+        <v>39</v>
+      </c>
+      <c r="M96" t="s">
         <v>43</v>
       </c>
       <c r="N96" s="2">
@@ -11625,7 +11624,7 @@
       <c r="B97" t="s">
         <v>37</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" t="s">
         <v>38</v>
       </c>
       <c r="D97" t="s">
@@ -11637,25 +11636,25 @@
       <c r="F97">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="G97" t="s">
         <v>34</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="H97" t="s">
         <v>35</v>
       </c>
-      <c r="I97" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J97" s="3" t="s">
+      <c r="I97" t="s">
+        <v>39</v>
+      </c>
+      <c r="J97" t="s">
         <v>40</v>
       </c>
       <c r="K97">
         <v>53216</v>
       </c>
-      <c r="L97" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M97" s="3" t="s">
+      <c r="L97" t="s">
+        <v>39</v>
+      </c>
+      <c r="M97" t="s">
         <v>43</v>
       </c>
       <c r="N97" s="2">
@@ -11738,7 +11737,7 @@
       <c r="B98" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" t="s">
         <v>38</v>
       </c>
       <c r="D98" t="s">
@@ -11750,25 +11749,25 @@
       <c r="F98">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="G98" t="s">
         <v>34</v>
       </c>
-      <c r="H98" s="3" t="s">
+      <c r="H98" t="s">
         <v>35</v>
       </c>
-      <c r="I98" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J98" s="3" t="s">
+      <c r="I98" t="s">
+        <v>39</v>
+      </c>
+      <c r="J98" t="s">
         <v>40</v>
       </c>
       <c r="K98">
         <v>53216</v>
       </c>
-      <c r="L98" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M98" s="3" t="s">
+      <c r="L98" t="s">
+        <v>39</v>
+      </c>
+      <c r="M98" t="s">
         <v>43</v>
       </c>
       <c r="N98" s="2">
@@ -11851,7 +11850,7 @@
       <c r="B99" t="s">
         <v>37</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" t="s">
         <v>38</v>
       </c>
       <c r="D99" t="s">
@@ -11863,25 +11862,25 @@
       <c r="F99">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="G99" t="s">
         <v>34</v>
       </c>
-      <c r="H99" s="3" t="s">
+      <c r="H99" t="s">
         <v>35</v>
       </c>
-      <c r="I99" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J99" s="3" t="s">
+      <c r="I99" t="s">
+        <v>39</v>
+      </c>
+      <c r="J99" t="s">
         <v>40</v>
       </c>
       <c r="K99">
         <v>53216</v>
       </c>
-      <c r="L99" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M99" s="3" t="s">
+      <c r="L99" t="s">
+        <v>39</v>
+      </c>
+      <c r="M99" t="s">
         <v>43</v>
       </c>
       <c r="N99" s="2">
@@ -11964,7 +11963,7 @@
       <c r="B100" t="s">
         <v>37</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" t="s">
         <v>38</v>
       </c>
       <c r="D100" t="s">
@@ -11976,25 +11975,25 @@
       <c r="F100">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="G100" t="s">
         <v>34</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" t="s">
         <v>35</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J100" s="3" t="s">
+      <c r="I100" t="s">
+        <v>39</v>
+      </c>
+      <c r="J100" t="s">
         <v>40</v>
       </c>
       <c r="K100">
         <v>53216</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M100" s="3" t="s">
+      <c r="L100" t="s">
+        <v>39</v>
+      </c>
+      <c r="M100" t="s">
         <v>43</v>
       </c>
       <c r="N100" s="2">
@@ -12077,7 +12076,7 @@
       <c r="B101" t="s">
         <v>37</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" t="s">
         <v>38</v>
       </c>
       <c r="D101" t="s">
@@ -12089,25 +12088,25 @@
       <c r="F101">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" t="s">
         <v>34</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="H101" t="s">
         <v>35</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J101" s="3" t="s">
+      <c r="I101" t="s">
+        <v>39</v>
+      </c>
+      <c r="J101" t="s">
         <v>40</v>
       </c>
       <c r="K101">
         <v>53216</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M101" s="3" t="s">
+      <c r="L101" t="s">
+        <v>39</v>
+      </c>
+      <c r="M101" t="s">
         <v>43</v>
       </c>
       <c r="N101" s="2">
@@ -12190,7 +12189,7 @@
       <c r="B102" t="s">
         <v>37</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" t="s">
         <v>38</v>
       </c>
       <c r="D102" t="s">
@@ -12202,25 +12201,25 @@
       <c r="F102">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="G102" t="s">
         <v>34</v>
       </c>
-      <c r="H102" s="3" t="s">
+      <c r="H102" t="s">
         <v>35</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J102" s="3" t="s">
+      <c r="I102" t="s">
+        <v>39</v>
+      </c>
+      <c r="J102" t="s">
         <v>40</v>
       </c>
       <c r="K102">
         <v>53216</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M102" s="3" t="s">
+      <c r="L102" t="s">
+        <v>39</v>
+      </c>
+      <c r="M102" t="s">
         <v>43</v>
       </c>
       <c r="N102" s="2">
@@ -12303,7 +12302,7 @@
       <c r="B103" t="s">
         <v>37</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" t="s">
         <v>38</v>
       </c>
       <c r="D103" t="s">
@@ -12315,25 +12314,25 @@
       <c r="F103">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="G103" t="s">
         <v>34</v>
       </c>
-      <c r="H103" s="3" t="s">
+      <c r="H103" t="s">
         <v>35</v>
       </c>
-      <c r="I103" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J103" s="3" t="s">
+      <c r="I103" t="s">
+        <v>39</v>
+      </c>
+      <c r="J103" t="s">
         <v>40</v>
       </c>
       <c r="K103">
         <v>53216</v>
       </c>
-      <c r="L103" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M103" s="3" t="s">
+      <c r="L103" t="s">
+        <v>39</v>
+      </c>
+      <c r="M103" t="s">
         <v>43</v>
       </c>
       <c r="N103" s="2">
@@ -12416,7 +12415,7 @@
       <c r="B104" t="s">
         <v>37</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" t="s">
         <v>38</v>
       </c>
       <c r="D104" t="s">
@@ -12428,25 +12427,25 @@
       <c r="F104">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="G104" t="s">
         <v>34</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="H104" t="s">
         <v>35</v>
       </c>
-      <c r="I104" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J104" s="3" t="s">
+      <c r="I104" t="s">
+        <v>39</v>
+      </c>
+      <c r="J104" t="s">
         <v>40</v>
       </c>
       <c r="K104">
         <v>53216</v>
       </c>
-      <c r="L104" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M104" s="3" t="s">
+      <c r="L104" t="s">
+        <v>39</v>
+      </c>
+      <c r="M104" t="s">
         <v>43</v>
       </c>
       <c r="N104" s="2">
@@ -12529,7 +12528,7 @@
       <c r="B105" t="s">
         <v>37</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" t="s">
         <v>38</v>
       </c>
       <c r="D105" t="s">
@@ -12541,25 +12540,25 @@
       <c r="F105">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="G105" t="s">
         <v>34</v>
       </c>
-      <c r="H105" s="3" t="s">
+      <c r="H105" t="s">
         <v>35</v>
       </c>
-      <c r="I105" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J105" s="3" t="s">
+      <c r="I105" t="s">
+        <v>39</v>
+      </c>
+      <c r="J105" t="s">
         <v>40</v>
       </c>
       <c r="K105">
         <v>53216</v>
       </c>
-      <c r="L105" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M105" s="3" t="s">
+      <c r="L105" t="s">
+        <v>39</v>
+      </c>
+      <c r="M105" t="s">
         <v>43</v>
       </c>
       <c r="N105" s="2">
@@ -12642,7 +12641,7 @@
       <c r="B106" t="s">
         <v>37</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" t="s">
         <v>38</v>
       </c>
       <c r="D106" t="s">
@@ -12654,25 +12653,25 @@
       <c r="F106">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="G106" t="s">
         <v>34</v>
       </c>
-      <c r="H106" s="3" t="s">
+      <c r="H106" t="s">
         <v>35</v>
       </c>
-      <c r="I106" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J106" s="3" t="s">
+      <c r="I106" t="s">
+        <v>39</v>
+      </c>
+      <c r="J106" t="s">
         <v>40</v>
       </c>
       <c r="K106">
         <v>53216</v>
       </c>
-      <c r="L106" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M106" s="3" t="s">
+      <c r="L106" t="s">
+        <v>39</v>
+      </c>
+      <c r="M106" t="s">
         <v>43</v>
       </c>
       <c r="N106" s="2">
@@ -12755,7 +12754,7 @@
       <c r="B107" t="s">
         <v>37</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" t="s">
         <v>38</v>
       </c>
       <c r="D107" t="s">
@@ -12767,25 +12766,25 @@
       <c r="F107">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="G107" t="s">
         <v>34</v>
       </c>
-      <c r="H107" s="3" t="s">
+      <c r="H107" t="s">
         <v>35</v>
       </c>
-      <c r="I107" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J107" s="3" t="s">
+      <c r="I107" t="s">
+        <v>39</v>
+      </c>
+      <c r="J107" t="s">
         <v>40</v>
       </c>
       <c r="K107">
         <v>53216</v>
       </c>
-      <c r="L107" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M107" s="3" t="s">
+      <c r="L107" t="s">
+        <v>39</v>
+      </c>
+      <c r="M107" t="s">
         <v>43</v>
       </c>
       <c r="N107" s="2">
@@ -12868,7 +12867,7 @@
       <c r="B108" t="s">
         <v>37</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" t="s">
         <v>38</v>
       </c>
       <c r="D108" t="s">
@@ -12880,25 +12879,25 @@
       <c r="F108">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="G108" t="s">
         <v>34</v>
       </c>
-      <c r="H108" s="3" t="s">
+      <c r="H108" t="s">
         <v>35</v>
       </c>
-      <c r="I108" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J108" s="3" t="s">
+      <c r="I108" t="s">
+        <v>39</v>
+      </c>
+      <c r="J108" t="s">
         <v>40</v>
       </c>
       <c r="K108">
         <v>53216</v>
       </c>
-      <c r="L108" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M108" s="3" t="s">
+      <c r="L108" t="s">
+        <v>39</v>
+      </c>
+      <c r="M108" t="s">
         <v>43</v>
       </c>
       <c r="N108" s="2">
@@ -12981,7 +12980,7 @@
       <c r="B109" t="s">
         <v>37</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" t="s">
         <v>38</v>
       </c>
       <c r="D109" t="s">
@@ -12993,25 +12992,25 @@
       <c r="F109">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="G109" t="s">
         <v>34</v>
       </c>
-      <c r="H109" s="3" t="s">
+      <c r="H109" t="s">
         <v>35</v>
       </c>
-      <c r="I109" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J109" s="3" t="s">
+      <c r="I109" t="s">
+        <v>39</v>
+      </c>
+      <c r="J109" t="s">
         <v>40</v>
       </c>
       <c r="K109">
         <v>53216</v>
       </c>
-      <c r="L109" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M109" s="3" t="s">
+      <c r="L109" t="s">
+        <v>39</v>
+      </c>
+      <c r="M109" t="s">
         <v>43</v>
       </c>
       <c r="N109" s="2">
@@ -13094,7 +13093,7 @@
       <c r="B110" t="s">
         <v>37</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" t="s">
         <v>38</v>
       </c>
       <c r="D110" t="s">
@@ -13106,25 +13105,25 @@
       <c r="F110">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="G110" t="s">
         <v>34</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="H110" t="s">
         <v>35</v>
       </c>
-      <c r="I110" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J110" s="3" t="s">
+      <c r="I110" t="s">
+        <v>39</v>
+      </c>
+      <c r="J110" t="s">
         <v>40</v>
       </c>
       <c r="K110">
         <v>53216</v>
       </c>
-      <c r="L110" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M110" s="3" t="s">
+      <c r="L110" t="s">
+        <v>39</v>
+      </c>
+      <c r="M110" t="s">
         <v>43</v>
       </c>
       <c r="N110" s="2">
@@ -13207,7 +13206,7 @@
       <c r="B111" t="s">
         <v>37</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" t="s">
         <v>38</v>
       </c>
       <c r="D111" t="s">
@@ -13219,25 +13218,25 @@
       <c r="F111">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="G111" t="s">
         <v>34</v>
       </c>
-      <c r="H111" s="3" t="s">
+      <c r="H111" t="s">
         <v>35</v>
       </c>
-      <c r="I111" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J111" s="3" t="s">
+      <c r="I111" t="s">
+        <v>39</v>
+      </c>
+      <c r="J111" t="s">
         <v>40</v>
       </c>
       <c r="K111">
         <v>53216</v>
       </c>
-      <c r="L111" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M111" s="3" t="s">
+      <c r="L111" t="s">
+        <v>39</v>
+      </c>
+      <c r="M111" t="s">
         <v>43</v>
       </c>
       <c r="N111" s="2">
@@ -13320,7 +13319,7 @@
       <c r="B112" t="s">
         <v>37</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" t="s">
         <v>38</v>
       </c>
       <c r="D112" t="s">
@@ -13332,25 +13331,25 @@
       <c r="F112">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="G112" t="s">
         <v>34</v>
       </c>
-      <c r="H112" s="3" t="s">
+      <c r="H112" t="s">
         <v>35</v>
       </c>
-      <c r="I112" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J112" s="3" t="s">
+      <c r="I112" t="s">
+        <v>39</v>
+      </c>
+      <c r="J112" t="s">
         <v>40</v>
       </c>
       <c r="K112">
         <v>53216</v>
       </c>
-      <c r="L112" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M112" s="3" t="s">
+      <c r="L112" t="s">
+        <v>39</v>
+      </c>
+      <c r="M112" t="s">
         <v>43</v>
       </c>
       <c r="N112" s="2">
@@ -13433,7 +13432,7 @@
       <c r="B113" t="s">
         <v>37</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" t="s">
         <v>38</v>
       </c>
       <c r="D113" t="s">
@@ -13445,25 +13444,25 @@
       <c r="F113">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="G113" t="s">
         <v>34</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="H113" t="s">
         <v>35</v>
       </c>
-      <c r="I113" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J113" s="3" t="s">
+      <c r="I113" t="s">
+        <v>39</v>
+      </c>
+      <c r="J113" t="s">
         <v>40</v>
       </c>
       <c r="K113">
         <v>53216</v>
       </c>
-      <c r="L113" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M113" s="3" t="s">
+      <c r="L113" t="s">
+        <v>39</v>
+      </c>
+      <c r="M113" t="s">
         <v>43</v>
       </c>
       <c r="N113" s="2">
@@ -13546,7 +13545,7 @@
       <c r="B114" t="s">
         <v>37</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" t="s">
         <v>38</v>
       </c>
       <c r="D114" t="s">
@@ -13558,25 +13557,25 @@
       <c r="F114">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="G114" t="s">
         <v>34</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="H114" t="s">
         <v>35</v>
       </c>
-      <c r="I114" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J114" s="3" t="s">
+      <c r="I114" t="s">
+        <v>39</v>
+      </c>
+      <c r="J114" t="s">
         <v>40</v>
       </c>
       <c r="K114">
         <v>53216</v>
       </c>
-      <c r="L114" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M114" s="3" t="s">
+      <c r="L114" t="s">
+        <v>39</v>
+      </c>
+      <c r="M114" t="s">
         <v>43</v>
       </c>
       <c r="N114" s="2">
@@ -13659,7 +13658,7 @@
       <c r="B115" t="s">
         <v>37</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" t="s">
         <v>38</v>
       </c>
       <c r="D115" t="s">
@@ -13671,25 +13670,25 @@
       <c r="F115">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G115" t="s">
         <v>34</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="H115" t="s">
         <v>35</v>
       </c>
-      <c r="I115" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J115" s="3" t="s">
+      <c r="I115" t="s">
+        <v>39</v>
+      </c>
+      <c r="J115" t="s">
         <v>40</v>
       </c>
       <c r="K115">
         <v>53216</v>
       </c>
-      <c r="L115" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M115" s="3" t="s">
+      <c r="L115" t="s">
+        <v>39</v>
+      </c>
+      <c r="M115" t="s">
         <v>43</v>
       </c>
       <c r="N115" s="2">
@@ -13772,7 +13771,7 @@
       <c r="B116" t="s">
         <v>37</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" t="s">
         <v>38</v>
       </c>
       <c r="D116" t="s">
@@ -13784,25 +13783,25 @@
       <c r="F116">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G116" t="s">
         <v>34</v>
       </c>
-      <c r="H116" s="3" t="s">
+      <c r="H116" t="s">
         <v>35</v>
       </c>
-      <c r="I116" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J116" s="3" t="s">
+      <c r="I116" t="s">
+        <v>39</v>
+      </c>
+      <c r="J116" t="s">
         <v>40</v>
       </c>
       <c r="K116">
         <v>53216</v>
       </c>
-      <c r="L116" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M116" s="3" t="s">
+      <c r="L116" t="s">
+        <v>39</v>
+      </c>
+      <c r="M116" t="s">
         <v>43</v>
       </c>
       <c r="N116" s="2">
@@ -13885,7 +13884,7 @@
       <c r="B117" t="s">
         <v>37</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" t="s">
         <v>38</v>
       </c>
       <c r="D117" t="s">
@@ -13897,25 +13896,25 @@
       <c r="F117">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" t="s">
         <v>34</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="H117" t="s">
         <v>35</v>
       </c>
-      <c r="I117" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J117" s="3" t="s">
+      <c r="I117" t="s">
+        <v>39</v>
+      </c>
+      <c r="J117" t="s">
         <v>40</v>
       </c>
       <c r="K117">
         <v>53216</v>
       </c>
-      <c r="L117" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M117" s="3" t="s">
+      <c r="L117" t="s">
+        <v>39</v>
+      </c>
+      <c r="M117" t="s">
         <v>43</v>
       </c>
       <c r="N117" s="2">
@@ -13998,7 +13997,7 @@
       <c r="B118" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" t="s">
         <v>38</v>
       </c>
       <c r="D118" t="s">
@@ -14010,25 +14009,25 @@
       <c r="F118">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G118" t="s">
         <v>34</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H118" t="s">
         <v>35</v>
       </c>
-      <c r="I118" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J118" s="3" t="s">
+      <c r="I118" t="s">
+        <v>39</v>
+      </c>
+      <c r="J118" t="s">
         <v>40</v>
       </c>
       <c r="K118">
         <v>53216</v>
       </c>
-      <c r="L118" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M118" s="3" t="s">
+      <c r="L118" t="s">
+        <v>39</v>
+      </c>
+      <c r="M118" t="s">
         <v>43</v>
       </c>
       <c r="N118" s="2">
@@ -14111,7 +14110,7 @@
       <c r="B119" t="s">
         <v>37</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" t="s">
         <v>38</v>
       </c>
       <c r="D119" t="s">
@@ -14123,25 +14122,25 @@
       <c r="F119">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" t="s">
         <v>34</v>
       </c>
-      <c r="H119" s="3" t="s">
+      <c r="H119" t="s">
         <v>35</v>
       </c>
-      <c r="I119" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J119" s="3" t="s">
+      <c r="I119" t="s">
+        <v>39</v>
+      </c>
+      <c r="J119" t="s">
         <v>40</v>
       </c>
       <c r="K119">
         <v>53216</v>
       </c>
-      <c r="L119" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M119" s="3" t="s">
+      <c r="L119" t="s">
+        <v>39</v>
+      </c>
+      <c r="M119" t="s">
         <v>43</v>
       </c>
       <c r="N119" s="2">
@@ -14224,7 +14223,7 @@
       <c r="B120" t="s">
         <v>37</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" t="s">
         <v>38</v>
       </c>
       <c r="D120" t="s">
@@ -14236,25 +14235,25 @@
       <c r="F120">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G120" t="s">
         <v>34</v>
       </c>
-      <c r="H120" s="3" t="s">
+      <c r="H120" t="s">
         <v>35</v>
       </c>
-      <c r="I120" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J120" s="3" t="s">
+      <c r="I120" t="s">
+        <v>39</v>
+      </c>
+      <c r="J120" t="s">
         <v>40</v>
       </c>
       <c r="K120">
         <v>53216</v>
       </c>
-      <c r="L120" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M120" s="3" t="s">
+      <c r="L120" t="s">
+        <v>39</v>
+      </c>
+      <c r="M120" t="s">
         <v>43</v>
       </c>
       <c r="N120" s="2">
@@ -14337,7 +14336,7 @@
       <c r="B121" t="s">
         <v>37</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" t="s">
         <v>38</v>
       </c>
       <c r="D121" t="s">
@@ -14349,25 +14348,25 @@
       <c r="F121">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" t="s">
         <v>34</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="H121" t="s">
         <v>35</v>
       </c>
-      <c r="I121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J121" s="3" t="s">
+      <c r="I121" t="s">
+        <v>39</v>
+      </c>
+      <c r="J121" t="s">
         <v>40</v>
       </c>
       <c r="K121">
         <v>53216</v>
       </c>
-      <c r="L121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M121" s="3" t="s">
+      <c r="L121" t="s">
+        <v>39</v>
+      </c>
+      <c r="M121" t="s">
         <v>43</v>
       </c>
       <c r="N121" s="2">
@@ -14450,7 +14449,7 @@
       <c r="B122" t="s">
         <v>37</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" t="s">
         <v>38</v>
       </c>
       <c r="D122" t="s">
@@ -14462,25 +14461,25 @@
       <c r="F122">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G122" t="s">
         <v>34</v>
       </c>
-      <c r="H122" s="3" t="s">
+      <c r="H122" t="s">
         <v>35</v>
       </c>
-      <c r="I122" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J122" s="3" t="s">
+      <c r="I122" t="s">
+        <v>39</v>
+      </c>
+      <c r="J122" t="s">
         <v>40</v>
       </c>
       <c r="K122">
         <v>53216</v>
       </c>
-      <c r="L122" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M122" s="3" t="s">
+      <c r="L122" t="s">
+        <v>39</v>
+      </c>
+      <c r="M122" t="s">
         <v>43</v>
       </c>
       <c r="N122" s="2">
@@ -14563,7 +14562,7 @@
       <c r="B123" t="s">
         <v>37</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" t="s">
         <v>38</v>
       </c>
       <c r="D123" t="s">
@@ -14575,25 +14574,25 @@
       <c r="F123">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="G123" t="s">
         <v>34</v>
       </c>
-      <c r="H123" s="3" t="s">
+      <c r="H123" t="s">
         <v>35</v>
       </c>
-      <c r="I123" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J123" s="3" t="s">
+      <c r="I123" t="s">
+        <v>39</v>
+      </c>
+      <c r="J123" t="s">
         <v>40</v>
       </c>
       <c r="K123">
         <v>53216</v>
       </c>
-      <c r="L123" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M123" s="3" t="s">
+      <c r="L123" t="s">
+        <v>39</v>
+      </c>
+      <c r="M123" t="s">
         <v>43</v>
       </c>
       <c r="N123" s="2">
@@ -14676,7 +14675,7 @@
       <c r="B124" t="s">
         <v>37</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" t="s">
         <v>38</v>
       </c>
       <c r="D124" t="s">
@@ -14688,25 +14687,25 @@
       <c r="F124">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="G124" t="s">
         <v>34</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="H124" t="s">
         <v>35</v>
       </c>
-      <c r="I124" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J124" s="3" t="s">
+      <c r="I124" t="s">
+        <v>39</v>
+      </c>
+      <c r="J124" t="s">
         <v>40</v>
       </c>
       <c r="K124">
         <v>53216</v>
       </c>
-      <c r="L124" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M124" s="3" t="s">
+      <c r="L124" t="s">
+        <v>39</v>
+      </c>
+      <c r="M124" t="s">
         <v>43</v>
       </c>
       <c r="N124" s="2">
@@ -14789,7 +14788,7 @@
       <c r="B125" t="s">
         <v>37</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" t="s">
         <v>38</v>
       </c>
       <c r="D125" t="s">
@@ -14801,25 +14800,25 @@
       <c r="F125">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="G125" t="s">
         <v>34</v>
       </c>
-      <c r="H125" s="3" t="s">
+      <c r="H125" t="s">
         <v>35</v>
       </c>
-      <c r="I125" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J125" s="3" t="s">
+      <c r="I125" t="s">
+        <v>39</v>
+      </c>
+      <c r="J125" t="s">
         <v>40</v>
       </c>
       <c r="K125">
         <v>53216</v>
       </c>
-      <c r="L125" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M125" s="3" t="s">
+      <c r="L125" t="s">
+        <v>39</v>
+      </c>
+      <c r="M125" t="s">
         <v>43</v>
       </c>
       <c r="N125" s="2">
@@ -14902,7 +14901,7 @@
       <c r="B126" t="s">
         <v>37</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="C126" t="s">
         <v>38</v>
       </c>
       <c r="D126" t="s">
@@ -14914,25 +14913,25 @@
       <c r="F126">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G126" s="3" t="s">
+      <c r="G126" t="s">
         <v>34</v>
       </c>
-      <c r="H126" s="3" t="s">
+      <c r="H126" t="s">
         <v>35</v>
       </c>
-      <c r="I126" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J126" s="3" t="s">
+      <c r="I126" t="s">
+        <v>39</v>
+      </c>
+      <c r="J126" t="s">
         <v>40</v>
       </c>
       <c r="K126">
         <v>53216</v>
       </c>
-      <c r="L126" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M126" s="3" t="s">
+      <c r="L126" t="s">
+        <v>39</v>
+      </c>
+      <c r="M126" t="s">
         <v>43</v>
       </c>
       <c r="N126" s="2">
@@ -15015,7 +15014,7 @@
       <c r="B127" t="s">
         <v>37</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" t="s">
         <v>38</v>
       </c>
       <c r="D127" t="s">
@@ -15027,25 +15026,25 @@
       <c r="F127">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G127" s="3" t="s">
+      <c r="G127" t="s">
         <v>34</v>
       </c>
-      <c r="H127" s="3" t="s">
+      <c r="H127" t="s">
         <v>35</v>
       </c>
-      <c r="I127" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J127" s="3" t="s">
+      <c r="I127" t="s">
+        <v>39</v>
+      </c>
+      <c r="J127" t="s">
         <v>40</v>
       </c>
       <c r="K127">
         <v>53216</v>
       </c>
-      <c r="L127" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M127" s="3" t="s">
+      <c r="L127" t="s">
+        <v>39</v>
+      </c>
+      <c r="M127" t="s">
         <v>43</v>
       </c>
       <c r="N127" s="2">
@@ -15128,7 +15127,7 @@
       <c r="B128" t="s">
         <v>37</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="C128" t="s">
         <v>38</v>
       </c>
       <c r="D128" t="s">
@@ -15140,25 +15139,25 @@
       <c r="F128">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G128" s="3" t="s">
+      <c r="G128" t="s">
         <v>34</v>
       </c>
-      <c r="H128" s="3" t="s">
+      <c r="H128" t="s">
         <v>35</v>
       </c>
-      <c r="I128" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J128" s="3" t="s">
+      <c r="I128" t="s">
+        <v>39</v>
+      </c>
+      <c r="J128" t="s">
         <v>40</v>
       </c>
       <c r="K128">
         <v>53216</v>
       </c>
-      <c r="L128" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M128" s="3" t="s">
+      <c r="L128" t="s">
+        <v>39</v>
+      </c>
+      <c r="M128" t="s">
         <v>43</v>
       </c>
       <c r="N128" s="2">
@@ -15241,7 +15240,7 @@
       <c r="B129" t="s">
         <v>37</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" t="s">
         <v>38</v>
       </c>
       <c r="D129" t="s">
@@ -15253,25 +15252,25 @@
       <c r="F129">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="G129" t="s">
         <v>34</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="H129" t="s">
         <v>35</v>
       </c>
-      <c r="I129" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J129" s="3" t="s">
+      <c r="I129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J129" t="s">
         <v>40</v>
       </c>
       <c r="K129">
         <v>53216</v>
       </c>
-      <c r="L129" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M129" s="3" t="s">
+      <c r="L129" t="s">
+        <v>39</v>
+      </c>
+      <c r="M129" t="s">
         <v>43</v>
       </c>
       <c r="N129" s="2">
@@ -15354,7 +15353,7 @@
       <c r="B130" t="s">
         <v>37</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" t="s">
         <v>38</v>
       </c>
       <c r="D130" t="s">
@@ -15366,25 +15365,25 @@
       <c r="F130">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="G130" t="s">
         <v>34</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="H130" t="s">
         <v>35</v>
       </c>
-      <c r="I130" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J130" s="3" t="s">
+      <c r="I130" t="s">
+        <v>39</v>
+      </c>
+      <c r="J130" t="s">
         <v>40</v>
       </c>
       <c r="K130">
         <v>53216</v>
       </c>
-      <c r="L130" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M130" s="3" t="s">
+      <c r="L130" t="s">
+        <v>39</v>
+      </c>
+      <c r="M130" t="s">
         <v>43</v>
       </c>
       <c r="N130" s="2">
@@ -15467,7 +15466,7 @@
       <c r="B131" t="s">
         <v>37</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" t="s">
         <v>38</v>
       </c>
       <c r="D131" t="s">
@@ -15479,25 +15478,25 @@
       <c r="F131">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="G131" t="s">
         <v>34</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="H131" t="s">
         <v>35</v>
       </c>
-      <c r="I131" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J131" s="3" t="s">
+      <c r="I131" t="s">
+        <v>39</v>
+      </c>
+      <c r="J131" t="s">
         <v>40</v>
       </c>
       <c r="K131">
         <v>53216</v>
       </c>
-      <c r="L131" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M131" s="3" t="s">
+      <c r="L131" t="s">
+        <v>39</v>
+      </c>
+      <c r="M131" t="s">
         <v>43</v>
       </c>
       <c r="N131" s="2">
@@ -15580,7 +15579,7 @@
       <c r="B132" t="s">
         <v>37</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C132" t="s">
         <v>38</v>
       </c>
       <c r="D132" t="s">
@@ -15592,25 +15591,25 @@
       <c r="F132">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G132" s="3" t="s">
+      <c r="G132" t="s">
         <v>34</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="H132" t="s">
         <v>35</v>
       </c>
-      <c r="I132" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J132" s="3" t="s">
+      <c r="I132" t="s">
+        <v>39</v>
+      </c>
+      <c r="J132" t="s">
         <v>40</v>
       </c>
       <c r="K132">
         <v>53216</v>
       </c>
-      <c r="L132" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M132" s="3" t="s">
+      <c r="L132" t="s">
+        <v>39</v>
+      </c>
+      <c r="M132" t="s">
         <v>43</v>
       </c>
       <c r="N132" s="2">
@@ -15693,7 +15692,7 @@
       <c r="B133" t="s">
         <v>37</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C133" t="s">
         <v>38</v>
       </c>
       <c r="D133" t="s">
@@ -15705,25 +15704,25 @@
       <c r="F133">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="G133" t="s">
         <v>34</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="H133" t="s">
         <v>35</v>
       </c>
-      <c r="I133" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J133" s="3" t="s">
+      <c r="I133" t="s">
+        <v>39</v>
+      </c>
+      <c r="J133" t="s">
         <v>40</v>
       </c>
       <c r="K133">
         <v>53216</v>
       </c>
-      <c r="L133" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M133" s="3" t="s">
+      <c r="L133" t="s">
+        <v>39</v>
+      </c>
+      <c r="M133" t="s">
         <v>43</v>
       </c>
       <c r="N133" s="2">
@@ -15806,7 +15805,7 @@
       <c r="B134" t="s">
         <v>37</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="C134" t="s">
         <v>38</v>
       </c>
       <c r="D134" t="s">
@@ -15818,25 +15817,25 @@
       <c r="F134">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G134" s="3" t="s">
+      <c r="G134" t="s">
         <v>34</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="H134" t="s">
         <v>35</v>
       </c>
-      <c r="I134" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J134" s="3" t="s">
+      <c r="I134" t="s">
+        <v>39</v>
+      </c>
+      <c r="J134" t="s">
         <v>40</v>
       </c>
       <c r="K134">
         <v>53216</v>
       </c>
-      <c r="L134" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M134" s="3" t="s">
+      <c r="L134" t="s">
+        <v>39</v>
+      </c>
+      <c r="M134" t="s">
         <v>43</v>
       </c>
       <c r="N134" s="2">
@@ -15919,7 +15918,7 @@
       <c r="B135" t="s">
         <v>37</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" t="s">
         <v>38</v>
       </c>
       <c r="D135" t="s">
@@ -15931,25 +15930,25 @@
       <c r="F135">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" t="s">
         <v>34</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="H135" t="s">
         <v>35</v>
       </c>
-      <c r="I135" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J135" s="3" t="s">
+      <c r="I135" t="s">
+        <v>39</v>
+      </c>
+      <c r="J135" t="s">
         <v>40</v>
       </c>
       <c r="K135">
         <v>53216</v>
       </c>
-      <c r="L135" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M135" s="3" t="s">
+      <c r="L135" t="s">
+        <v>39</v>
+      </c>
+      <c r="M135" t="s">
         <v>43</v>
       </c>
       <c r="N135" s="2">
@@ -16032,7 +16031,7 @@
       <c r="B136" t="s">
         <v>37</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="C136" t="s">
         <v>38</v>
       </c>
       <c r="D136" t="s">
@@ -16044,25 +16043,25 @@
       <c r="F136">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G136" s="3" t="s">
+      <c r="G136" t="s">
         <v>34</v>
       </c>
-      <c r="H136" s="3" t="s">
+      <c r="H136" t="s">
         <v>35</v>
       </c>
-      <c r="I136" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J136" s="3" t="s">
+      <c r="I136" t="s">
+        <v>39</v>
+      </c>
+      <c r="J136" t="s">
         <v>40</v>
       </c>
       <c r="K136">
         <v>53216</v>
       </c>
-      <c r="L136" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M136" s="3" t="s">
+      <c r="L136" t="s">
+        <v>39</v>
+      </c>
+      <c r="M136" t="s">
         <v>43</v>
       </c>
       <c r="N136" s="2">
@@ -16145,7 +16144,7 @@
       <c r="B137" t="s">
         <v>37</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" t="s">
         <v>38</v>
       </c>
       <c r="D137" t="s">
@@ -16157,25 +16156,25 @@
       <c r="F137">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="G137" t="s">
         <v>34</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="H137" t="s">
         <v>35</v>
       </c>
-      <c r="I137" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J137" s="3" t="s">
+      <c r="I137" t="s">
+        <v>39</v>
+      </c>
+      <c r="J137" t="s">
         <v>40</v>
       </c>
       <c r="K137">
         <v>53216</v>
       </c>
-      <c r="L137" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M137" s="3" t="s">
+      <c r="L137" t="s">
+        <v>39</v>
+      </c>
+      <c r="M137" t="s">
         <v>43</v>
       </c>
       <c r="N137" s="2">
@@ -16258,7 +16257,7 @@
       <c r="B138" t="s">
         <v>37</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" t="s">
         <v>38</v>
       </c>
       <c r="D138" t="s">
@@ -16270,25 +16269,25 @@
       <c r="F138">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G138" t="s">
         <v>34</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="H138" t="s">
         <v>35</v>
       </c>
-      <c r="I138" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J138" s="3" t="s">
+      <c r="I138" t="s">
+        <v>39</v>
+      </c>
+      <c r="J138" t="s">
         <v>40</v>
       </c>
       <c r="K138">
         <v>53216</v>
       </c>
-      <c r="L138" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M138" s="3" t="s">
+      <c r="L138" t="s">
+        <v>39</v>
+      </c>
+      <c r="M138" t="s">
         <v>43</v>
       </c>
       <c r="N138" s="2">
@@ -16371,7 +16370,7 @@
       <c r="B139" t="s">
         <v>37</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" t="s">
         <v>38</v>
       </c>
       <c r="D139" t="s">
@@ -16383,25 +16382,25 @@
       <c r="F139">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G139" s="3" t="s">
+      <c r="G139" t="s">
         <v>34</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="H139" t="s">
         <v>35</v>
       </c>
-      <c r="I139" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J139" s="3" t="s">
+      <c r="I139" t="s">
+        <v>39</v>
+      </c>
+      <c r="J139" t="s">
         <v>40</v>
       </c>
       <c r="K139">
         <v>53216</v>
       </c>
-      <c r="L139" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M139" s="3" t="s">
+      <c r="L139" t="s">
+        <v>39</v>
+      </c>
+      <c r="M139" t="s">
         <v>43</v>
       </c>
       <c r="N139" s="2">
@@ -16484,7 +16483,7 @@
       <c r="B140" t="s">
         <v>37</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" t="s">
         <v>38</v>
       </c>
       <c r="D140" t="s">
@@ -16496,25 +16495,25 @@
       <c r="F140">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="G140" t="s">
         <v>34</v>
       </c>
-      <c r="H140" s="3" t="s">
+      <c r="H140" t="s">
         <v>35</v>
       </c>
-      <c r="I140" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J140" s="3" t="s">
+      <c r="I140" t="s">
+        <v>39</v>
+      </c>
+      <c r="J140" t="s">
         <v>40</v>
       </c>
       <c r="K140">
         <v>53216</v>
       </c>
-      <c r="L140" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M140" s="3" t="s">
+      <c r="L140" t="s">
+        <v>39</v>
+      </c>
+      <c r="M140" t="s">
         <v>43</v>
       </c>
       <c r="N140" s="2">
@@ -16597,7 +16596,7 @@
       <c r="B141" t="s">
         <v>37</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" t="s">
         <v>38</v>
       </c>
       <c r="D141" t="s">
@@ -16609,25 +16608,25 @@
       <c r="F141">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G141" s="3" t="s">
+      <c r="G141" t="s">
         <v>34</v>
       </c>
-      <c r="H141" s="3" t="s">
+      <c r="H141" t="s">
         <v>35</v>
       </c>
-      <c r="I141" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J141" s="3" t="s">
+      <c r="I141" t="s">
+        <v>39</v>
+      </c>
+      <c r="J141" t="s">
         <v>40</v>
       </c>
       <c r="K141">
         <v>53216</v>
       </c>
-      <c r="L141" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M141" s="3" t="s">
+      <c r="L141" t="s">
+        <v>39</v>
+      </c>
+      <c r="M141" t="s">
         <v>43</v>
       </c>
       <c r="N141" s="2">
@@ -16710,7 +16709,7 @@
       <c r="B142" t="s">
         <v>37</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" t="s">
         <v>38</v>
       </c>
       <c r="D142" t="s">
@@ -16722,25 +16721,25 @@
       <c r="F142">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="G142" t="s">
         <v>34</v>
       </c>
-      <c r="H142" s="3" t="s">
+      <c r="H142" t="s">
         <v>35</v>
       </c>
-      <c r="I142" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J142" s="3" t="s">
+      <c r="I142" t="s">
+        <v>39</v>
+      </c>
+      <c r="J142" t="s">
         <v>40</v>
       </c>
       <c r="K142">
         <v>53216</v>
       </c>
-      <c r="L142" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M142" s="3" t="s">
+      <c r="L142" t="s">
+        <v>39</v>
+      </c>
+      <c r="M142" t="s">
         <v>43</v>
       </c>
       <c r="N142" s="2">
@@ -16823,7 +16822,7 @@
       <c r="B143" t="s">
         <v>37</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" t="s">
         <v>38</v>
       </c>
       <c r="D143" t="s">
@@ -16835,25 +16834,25 @@
       <c r="F143">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="G143" t="s">
         <v>34</v>
       </c>
-      <c r="H143" s="3" t="s">
+      <c r="H143" t="s">
         <v>35</v>
       </c>
-      <c r="I143" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J143" s="3" t="s">
+      <c r="I143" t="s">
+        <v>39</v>
+      </c>
+      <c r="J143" t="s">
         <v>40</v>
       </c>
       <c r="K143">
         <v>53216</v>
       </c>
-      <c r="L143" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M143" s="3" t="s">
+      <c r="L143" t="s">
+        <v>39</v>
+      </c>
+      <c r="M143" t="s">
         <v>43</v>
       </c>
       <c r="N143" s="2">
@@ -16936,7 +16935,7 @@
       <c r="B144" t="s">
         <v>37</v>
       </c>
-      <c r="C144" s="3" t="s">
+      <c r="C144" t="s">
         <v>38</v>
       </c>
       <c r="D144" t="s">
@@ -16948,25 +16947,25 @@
       <c r="F144">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" t="s">
         <v>34</v>
       </c>
-      <c r="H144" s="3" t="s">
+      <c r="H144" t="s">
         <v>35</v>
       </c>
-      <c r="I144" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J144" s="3" t="s">
+      <c r="I144" t="s">
+        <v>39</v>
+      </c>
+      <c r="J144" t="s">
         <v>40</v>
       </c>
       <c r="K144">
         <v>53216</v>
       </c>
-      <c r="L144" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M144" s="3" t="s">
+      <c r="L144" t="s">
+        <v>39</v>
+      </c>
+      <c r="M144" t="s">
         <v>43</v>
       </c>
       <c r="N144" s="2">
@@ -17049,7 +17048,7 @@
       <c r="B145" t="s">
         <v>37</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C145" t="s">
         <v>38</v>
       </c>
       <c r="D145" t="s">
@@ -17061,25 +17060,25 @@
       <c r="F145">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G145" t="s">
         <v>34</v>
       </c>
-      <c r="H145" s="3" t="s">
+      <c r="H145" t="s">
         <v>35</v>
       </c>
-      <c r="I145" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J145" s="3" t="s">
+      <c r="I145" t="s">
+        <v>39</v>
+      </c>
+      <c r="J145" t="s">
         <v>40</v>
       </c>
       <c r="K145">
         <v>53216</v>
       </c>
-      <c r="L145" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M145" s="3" t="s">
+      <c r="L145" t="s">
+        <v>39</v>
+      </c>
+      <c r="M145" t="s">
         <v>43</v>
       </c>
       <c r="N145" s="2">
@@ -17162,7 +17161,7 @@
       <c r="B146" t="s">
         <v>37</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C146" t="s">
         <v>38</v>
       </c>
       <c r="D146" t="s">
@@ -17174,25 +17173,25 @@
       <c r="F146">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="G146" t="s">
         <v>34</v>
       </c>
-      <c r="H146" s="3" t="s">
+      <c r="H146" t="s">
         <v>35</v>
       </c>
-      <c r="I146" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J146" s="3" t="s">
+      <c r="I146" t="s">
+        <v>39</v>
+      </c>
+      <c r="J146" t="s">
         <v>40</v>
       </c>
       <c r="K146">
         <v>53216</v>
       </c>
-      <c r="L146" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M146" s="3" t="s">
+      <c r="L146" t="s">
+        <v>39</v>
+      </c>
+      <c r="M146" t="s">
         <v>43</v>
       </c>
       <c r="N146" s="2">
@@ -17275,7 +17274,7 @@
       <c r="B147" t="s">
         <v>37</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="C147" t="s">
         <v>38</v>
       </c>
       <c r="D147" t="s">
@@ -17287,25 +17286,25 @@
       <c r="F147">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G147" s="3" t="s">
+      <c r="G147" t="s">
         <v>34</v>
       </c>
-      <c r="H147" s="3" t="s">
+      <c r="H147" t="s">
         <v>35</v>
       </c>
-      <c r="I147" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J147" s="3" t="s">
+      <c r="I147" t="s">
+        <v>39</v>
+      </c>
+      <c r="J147" t="s">
         <v>40</v>
       </c>
       <c r="K147">
         <v>53216</v>
       </c>
-      <c r="L147" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M147" s="3" t="s">
+      <c r="L147" t="s">
+        <v>39</v>
+      </c>
+      <c r="M147" t="s">
         <v>43</v>
       </c>
       <c r="N147" s="2">
@@ -17388,7 +17387,7 @@
       <c r="B148" t="s">
         <v>37</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C148" t="s">
         <v>38</v>
       </c>
       <c r="D148" t="s">
@@ -17400,25 +17399,25 @@
       <c r="F148">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G148" s="3" t="s">
+      <c r="G148" t="s">
         <v>34</v>
       </c>
-      <c r="H148" s="3" t="s">
+      <c r="H148" t="s">
         <v>35</v>
       </c>
-      <c r="I148" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J148" s="3" t="s">
+      <c r="I148" t="s">
+        <v>39</v>
+      </c>
+      <c r="J148" t="s">
         <v>40</v>
       </c>
       <c r="K148">
         <v>53216</v>
       </c>
-      <c r="L148" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M148" s="3" t="s">
+      <c r="L148" t="s">
+        <v>39</v>
+      </c>
+      <c r="M148" t="s">
         <v>43</v>
       </c>
       <c r="N148" s="2">
@@ -17501,7 +17500,7 @@
       <c r="B149" t="s">
         <v>37</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C149" t="s">
         <v>38</v>
       </c>
       <c r="D149" t="s">
@@ -17513,25 +17512,25 @@
       <c r="F149">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G149" s="3" t="s">
+      <c r="G149" t="s">
         <v>34</v>
       </c>
-      <c r="H149" s="3" t="s">
+      <c r="H149" t="s">
         <v>35</v>
       </c>
-      <c r="I149" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J149" s="3" t="s">
+      <c r="I149" t="s">
+        <v>39</v>
+      </c>
+      <c r="J149" t="s">
         <v>40</v>
       </c>
       <c r="K149">
         <v>53216</v>
       </c>
-      <c r="L149" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M149" s="3" t="s">
+      <c r="L149" t="s">
+        <v>39</v>
+      </c>
+      <c r="M149" t="s">
         <v>43</v>
       </c>
       <c r="N149" s="2">
@@ -17614,7 +17613,7 @@
       <c r="B150" t="s">
         <v>37</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C150" t="s">
         <v>38</v>
       </c>
       <c r="D150" t="s">
@@ -17626,25 +17625,25 @@
       <c r="F150">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G150" s="3" t="s">
+      <c r="G150" t="s">
         <v>34</v>
       </c>
-      <c r="H150" s="3" t="s">
+      <c r="H150" t="s">
         <v>35</v>
       </c>
-      <c r="I150" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J150" s="3" t="s">
+      <c r="I150" t="s">
+        <v>39</v>
+      </c>
+      <c r="J150" t="s">
         <v>40</v>
       </c>
       <c r="K150">
         <v>53216</v>
       </c>
-      <c r="L150" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M150" s="3" t="s">
+      <c r="L150" t="s">
+        <v>39</v>
+      </c>
+      <c r="M150" t="s">
         <v>43</v>
       </c>
       <c r="N150" s="2">
@@ -17727,7 +17726,7 @@
       <c r="B151" t="s">
         <v>37</v>
       </c>
-      <c r="C151" s="3" t="s">
+      <c r="C151" t="s">
         <v>38</v>
       </c>
       <c r="D151" t="s">
@@ -17739,25 +17738,25 @@
       <c r="F151">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G151" s="3" t="s">
+      <c r="G151" t="s">
         <v>34</v>
       </c>
-      <c r="H151" s="3" t="s">
+      <c r="H151" t="s">
         <v>35</v>
       </c>
-      <c r="I151" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J151" s="3" t="s">
+      <c r="I151" t="s">
+        <v>39</v>
+      </c>
+      <c r="J151" t="s">
         <v>40</v>
       </c>
       <c r="K151">
         <v>53216</v>
       </c>
-      <c r="L151" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M151" s="3" t="s">
+      <c r="L151" t="s">
+        <v>39</v>
+      </c>
+      <c r="M151" t="s">
         <v>43</v>
       </c>
       <c r="N151" s="2">
@@ -17840,7 +17839,7 @@
       <c r="B152" t="s">
         <v>37</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="C152" t="s">
         <v>38</v>
       </c>
       <c r="D152" t="s">
@@ -17852,25 +17851,25 @@
       <c r="F152">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G152" s="3" t="s">
+      <c r="G152" t="s">
         <v>34</v>
       </c>
-      <c r="H152" s="3" t="s">
+      <c r="H152" t="s">
         <v>35</v>
       </c>
-      <c r="I152" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J152" s="3" t="s">
+      <c r="I152" t="s">
+        <v>39</v>
+      </c>
+      <c r="J152" t="s">
         <v>40</v>
       </c>
       <c r="K152">
         <v>53216</v>
       </c>
-      <c r="L152" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M152" s="3" t="s">
+      <c r="L152" t="s">
+        <v>39</v>
+      </c>
+      <c r="M152" t="s">
         <v>43</v>
       </c>
       <c r="N152" s="2">
@@ -17953,7 +17952,7 @@
       <c r="B153" t="s">
         <v>37</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C153" t="s">
         <v>38</v>
       </c>
       <c r="D153" t="s">
@@ -17965,25 +17964,25 @@
       <c r="F153">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G153" s="3" t="s">
+      <c r="G153" t="s">
         <v>34</v>
       </c>
-      <c r="H153" s="3" t="s">
+      <c r="H153" t="s">
         <v>35</v>
       </c>
-      <c r="I153" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J153" s="3" t="s">
+      <c r="I153" t="s">
+        <v>39</v>
+      </c>
+      <c r="J153" t="s">
         <v>40</v>
       </c>
       <c r="K153">
         <v>53216</v>
       </c>
-      <c r="L153" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M153" s="3" t="s">
+      <c r="L153" t="s">
+        <v>39</v>
+      </c>
+      <c r="M153" t="s">
         <v>43</v>
       </c>
       <c r="N153" s="2">
@@ -18066,7 +18065,7 @@
       <c r="B154" t="s">
         <v>37</v>
       </c>
-      <c r="C154" s="3" t="s">
+      <c r="C154" t="s">
         <v>38</v>
       </c>
       <c r="D154" t="s">
@@ -18078,25 +18077,25 @@
       <c r="F154">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G154" s="3" t="s">
+      <c r="G154" t="s">
         <v>34</v>
       </c>
-      <c r="H154" s="3" t="s">
+      <c r="H154" t="s">
         <v>35</v>
       </c>
-      <c r="I154" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J154" s="3" t="s">
+      <c r="I154" t="s">
+        <v>39</v>
+      </c>
+      <c r="J154" t="s">
         <v>40</v>
       </c>
       <c r="K154">
         <v>53216</v>
       </c>
-      <c r="L154" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M154" s="3" t="s">
+      <c r="L154" t="s">
+        <v>39</v>
+      </c>
+      <c r="M154" t="s">
         <v>43</v>
       </c>
       <c r="N154" s="2">
@@ -18179,7 +18178,7 @@
       <c r="B155" t="s">
         <v>37</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="C155" t="s">
         <v>38</v>
       </c>
       <c r="D155" t="s">
@@ -18191,25 +18190,25 @@
       <c r="F155">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G155" s="3" t="s">
+      <c r="G155" t="s">
         <v>34</v>
       </c>
-      <c r="H155" s="3" t="s">
+      <c r="H155" t="s">
         <v>35</v>
       </c>
-      <c r="I155" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J155" s="3" t="s">
+      <c r="I155" t="s">
+        <v>39</v>
+      </c>
+      <c r="J155" t="s">
         <v>40</v>
       </c>
       <c r="K155">
         <v>53216</v>
       </c>
-      <c r="L155" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M155" s="3" t="s">
+      <c r="L155" t="s">
+        <v>39</v>
+      </c>
+      <c r="M155" t="s">
         <v>43</v>
       </c>
       <c r="N155" s="2">
@@ -18292,7 +18291,7 @@
       <c r="B156" t="s">
         <v>37</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="C156" t="s">
         <v>38</v>
       </c>
       <c r="D156" t="s">
@@ -18304,25 +18303,25 @@
       <c r="F156">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G156" s="3" t="s">
+      <c r="G156" t="s">
         <v>34</v>
       </c>
-      <c r="H156" s="3" t="s">
+      <c r="H156" t="s">
         <v>35</v>
       </c>
-      <c r="I156" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J156" s="3" t="s">
+      <c r="I156" t="s">
+        <v>39</v>
+      </c>
+      <c r="J156" t="s">
         <v>40</v>
       </c>
       <c r="K156">
         <v>53216</v>
       </c>
-      <c r="L156" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M156" s="3" t="s">
+      <c r="L156" t="s">
+        <v>39</v>
+      </c>
+      <c r="M156" t="s">
         <v>43</v>
       </c>
       <c r="N156" s="2">
@@ -18405,7 +18404,7 @@
       <c r="B157" t="s">
         <v>37</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C157" t="s">
         <v>38</v>
       </c>
       <c r="D157" t="s">
@@ -18417,25 +18416,25 @@
       <c r="F157">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G157" s="3" t="s">
+      <c r="G157" t="s">
         <v>34</v>
       </c>
-      <c r="H157" s="3" t="s">
+      <c r="H157" t="s">
         <v>35</v>
       </c>
-      <c r="I157" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J157" s="3" t="s">
+      <c r="I157" t="s">
+        <v>39</v>
+      </c>
+      <c r="J157" t="s">
         <v>40</v>
       </c>
       <c r="K157">
         <v>53216</v>
       </c>
-      <c r="L157" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M157" s="3" t="s">
+      <c r="L157" t="s">
+        <v>39</v>
+      </c>
+      <c r="M157" t="s">
         <v>43</v>
       </c>
       <c r="N157" s="2">
@@ -18518,7 +18517,7 @@
       <c r="B158" t="s">
         <v>37</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" t="s">
         <v>38</v>
       </c>
       <c r="D158" t="s">
@@ -18530,25 +18529,25 @@
       <c r="F158">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G158" s="3" t="s">
+      <c r="G158" t="s">
         <v>34</v>
       </c>
-      <c r="H158" s="3" t="s">
+      <c r="H158" t="s">
         <v>35</v>
       </c>
-      <c r="I158" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J158" s="3" t="s">
+      <c r="I158" t="s">
+        <v>39</v>
+      </c>
+      <c r="J158" t="s">
         <v>40</v>
       </c>
       <c r="K158">
         <v>53216</v>
       </c>
-      <c r="L158" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M158" s="3" t="s">
+      <c r="L158" t="s">
+        <v>39</v>
+      </c>
+      <c r="M158" t="s">
         <v>43</v>
       </c>
       <c r="N158" s="2">
@@ -18631,7 +18630,7 @@
       <c r="B159" t="s">
         <v>37</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C159" t="s">
         <v>38</v>
       </c>
       <c r="D159" t="s">
@@ -18643,25 +18642,25 @@
       <c r="F159">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G159" s="3" t="s">
+      <c r="G159" t="s">
         <v>34</v>
       </c>
-      <c r="H159" s="3" t="s">
+      <c r="H159" t="s">
         <v>35</v>
       </c>
-      <c r="I159" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J159" s="3" t="s">
+      <c r="I159" t="s">
+        <v>39</v>
+      </c>
+      <c r="J159" t="s">
         <v>40</v>
       </c>
       <c r="K159">
         <v>53216</v>
       </c>
-      <c r="L159" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M159" s="3" t="s">
+      <c r="L159" t="s">
+        <v>39</v>
+      </c>
+      <c r="M159" t="s">
         <v>43</v>
       </c>
       <c r="N159" s="2">
@@ -18744,7 +18743,7 @@
       <c r="B160" t="s">
         <v>37</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="C160" t="s">
         <v>38</v>
       </c>
       <c r="D160" t="s">
@@ -18756,25 +18755,25 @@
       <c r="F160">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="G160" t="s">
         <v>34</v>
       </c>
-      <c r="H160" s="3" t="s">
+      <c r="H160" t="s">
         <v>35</v>
       </c>
-      <c r="I160" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J160" s="3" t="s">
+      <c r="I160" t="s">
+        <v>39</v>
+      </c>
+      <c r="J160" t="s">
         <v>40</v>
       </c>
       <c r="K160">
         <v>53216</v>
       </c>
-      <c r="L160" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M160" s="3" t="s">
+      <c r="L160" t="s">
+        <v>39</v>
+      </c>
+      <c r="M160" t="s">
         <v>43</v>
       </c>
       <c r="N160" s="2">
@@ -18857,7 +18856,7 @@
       <c r="B161" t="s">
         <v>37</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" t="s">
         <v>38</v>
       </c>
       <c r="D161" t="s">
@@ -18869,25 +18868,25 @@
       <c r="F161">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G161" s="3" t="s">
+      <c r="G161" t="s">
         <v>34</v>
       </c>
-      <c r="H161" s="3" t="s">
+      <c r="H161" t="s">
         <v>35</v>
       </c>
-      <c r="I161" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J161" s="3" t="s">
+      <c r="I161" t="s">
+        <v>39</v>
+      </c>
+      <c r="J161" t="s">
         <v>40</v>
       </c>
       <c r="K161">
         <v>53216</v>
       </c>
-      <c r="L161" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M161" s="3" t="s">
+      <c r="L161" t="s">
+        <v>39</v>
+      </c>
+      <c r="M161" t="s">
         <v>43</v>
       </c>
       <c r="N161" s="2">
@@ -18970,7 +18969,7 @@
       <c r="B162" t="s">
         <v>37</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="C162" t="s">
         <v>38</v>
       </c>
       <c r="D162" t="s">
@@ -18982,25 +18981,25 @@
       <c r="F162">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G162" s="3" t="s">
+      <c r="G162" t="s">
         <v>34</v>
       </c>
-      <c r="H162" s="3" t="s">
+      <c r="H162" t="s">
         <v>35</v>
       </c>
-      <c r="I162" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J162" s="3" t="s">
+      <c r="I162" t="s">
+        <v>39</v>
+      </c>
+      <c r="J162" t="s">
         <v>40</v>
       </c>
       <c r="K162">
         <v>53216</v>
       </c>
-      <c r="L162" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M162" s="3" t="s">
+      <c r="L162" t="s">
+        <v>39</v>
+      </c>
+      <c r="M162" t="s">
         <v>43</v>
       </c>
       <c r="N162" s="2">
@@ -19083,7 +19082,7 @@
       <c r="B163" t="s">
         <v>37</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="C163" t="s">
         <v>38</v>
       </c>
       <c r="D163" t="s">
@@ -19095,25 +19094,25 @@
       <c r="F163">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G163" s="3" t="s">
+      <c r="G163" t="s">
         <v>34</v>
       </c>
-      <c r="H163" s="3" t="s">
+      <c r="H163" t="s">
         <v>35</v>
       </c>
-      <c r="I163" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J163" s="3" t="s">
+      <c r="I163" t="s">
+        <v>39</v>
+      </c>
+      <c r="J163" t="s">
         <v>40</v>
       </c>
       <c r="K163">
         <v>53216</v>
       </c>
-      <c r="L163" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M163" s="3" t="s">
+      <c r="L163" t="s">
+        <v>39</v>
+      </c>
+      <c r="M163" t="s">
         <v>43</v>
       </c>
       <c r="N163" s="2">
@@ -19196,7 +19195,7 @@
       <c r="B164" t="s">
         <v>37</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="C164" t="s">
         <v>38</v>
       </c>
       <c r="D164" t="s">
@@ -19208,25 +19207,25 @@
       <c r="F164">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G164" s="3" t="s">
+      <c r="G164" t="s">
         <v>34</v>
       </c>
-      <c r="H164" s="3" t="s">
+      <c r="H164" t="s">
         <v>35</v>
       </c>
-      <c r="I164" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J164" s="3" t="s">
+      <c r="I164" t="s">
+        <v>39</v>
+      </c>
+      <c r="J164" t="s">
         <v>40</v>
       </c>
       <c r="K164">
         <v>53216</v>
       </c>
-      <c r="L164" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M164" s="3" t="s">
+      <c r="L164" t="s">
+        <v>39</v>
+      </c>
+      <c r="M164" t="s">
         <v>43</v>
       </c>
       <c r="N164" s="2">
@@ -19309,7 +19308,7 @@
       <c r="B165" t="s">
         <v>37</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="C165" t="s">
         <v>38</v>
       </c>
       <c r="D165" t="s">
@@ -19321,25 +19320,25 @@
       <c r="F165">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G165" s="3" t="s">
+      <c r="G165" t="s">
         <v>34</v>
       </c>
-      <c r="H165" s="3" t="s">
+      <c r="H165" t="s">
         <v>35</v>
       </c>
-      <c r="I165" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J165" s="3" t="s">
+      <c r="I165" t="s">
+        <v>39</v>
+      </c>
+      <c r="J165" t="s">
         <v>40</v>
       </c>
       <c r="K165">
         <v>53216</v>
       </c>
-      <c r="L165" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M165" s="3" t="s">
+      <c r="L165" t="s">
+        <v>39</v>
+      </c>
+      <c r="M165" t="s">
         <v>43</v>
       </c>
       <c r="N165" s="2">
@@ -19422,7 +19421,7 @@
       <c r="B166" t="s">
         <v>37</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="C166" t="s">
         <v>38</v>
       </c>
       <c r="D166" t="s">
@@ -19434,25 +19433,25 @@
       <c r="F166">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G166" s="3" t="s">
+      <c r="G166" t="s">
         <v>34</v>
       </c>
-      <c r="H166" s="3" t="s">
+      <c r="H166" t="s">
         <v>35</v>
       </c>
-      <c r="I166" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J166" s="3" t="s">
+      <c r="I166" t="s">
+        <v>39</v>
+      </c>
+      <c r="J166" t="s">
         <v>40</v>
       </c>
       <c r="K166">
         <v>53216</v>
       </c>
-      <c r="L166" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M166" s="3" t="s">
+      <c r="L166" t="s">
+        <v>39</v>
+      </c>
+      <c r="M166" t="s">
         <v>43</v>
       </c>
       <c r="N166" s="2">
@@ -19535,7 +19534,7 @@
       <c r="B167" t="s">
         <v>37</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C167" t="s">
         <v>38</v>
       </c>
       <c r="D167" t="s">
@@ -19547,25 +19546,25 @@
       <c r="F167">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G167" s="3" t="s">
+      <c r="G167" t="s">
         <v>34</v>
       </c>
-      <c r="H167" s="3" t="s">
+      <c r="H167" t="s">
         <v>35</v>
       </c>
-      <c r="I167" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J167" s="3" t="s">
+      <c r="I167" t="s">
+        <v>39</v>
+      </c>
+      <c r="J167" t="s">
         <v>40</v>
       </c>
       <c r="K167">
         <v>53216</v>
       </c>
-      <c r="L167" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M167" s="3" t="s">
+      <c r="L167" t="s">
+        <v>39</v>
+      </c>
+      <c r="M167" t="s">
         <v>43</v>
       </c>
       <c r="N167" s="2">
@@ -19648,7 +19647,7 @@
       <c r="B168" t="s">
         <v>37</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="C168" t="s">
         <v>38</v>
       </c>
       <c r="D168" t="s">
@@ -19660,25 +19659,25 @@
       <c r="F168">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G168" s="3" t="s">
+      <c r="G168" t="s">
         <v>34</v>
       </c>
-      <c r="H168" s="3" t="s">
+      <c r="H168" t="s">
         <v>35</v>
       </c>
-      <c r="I168" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J168" s="3" t="s">
+      <c r="I168" t="s">
+        <v>39</v>
+      </c>
+      <c r="J168" t="s">
         <v>40</v>
       </c>
       <c r="K168">
         <v>53216</v>
       </c>
-      <c r="L168" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M168" s="3" t="s">
+      <c r="L168" t="s">
+        <v>39</v>
+      </c>
+      <c r="M168" t="s">
         <v>43</v>
       </c>
       <c r="N168" s="2">
@@ -19761,7 +19760,7 @@
       <c r="B169" t="s">
         <v>37</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C169" t="s">
         <v>38</v>
       </c>
       <c r="D169" t="s">
@@ -19773,25 +19772,25 @@
       <c r="F169">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G169" s="3" t="s">
+      <c r="G169" t="s">
         <v>34</v>
       </c>
-      <c r="H169" s="3" t="s">
+      <c r="H169" t="s">
         <v>35</v>
       </c>
-      <c r="I169" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J169" s="3" t="s">
+      <c r="I169" t="s">
+        <v>39</v>
+      </c>
+      <c r="J169" t="s">
         <v>40</v>
       </c>
       <c r="K169">
         <v>53216</v>
       </c>
-      <c r="L169" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M169" s="3" t="s">
+      <c r="L169" t="s">
+        <v>39</v>
+      </c>
+      <c r="M169" t="s">
         <v>43</v>
       </c>
       <c r="N169" s="2">
@@ -19874,7 +19873,7 @@
       <c r="B170" t="s">
         <v>37</v>
       </c>
-      <c r="C170" s="3" t="s">
+      <c r="C170" t="s">
         <v>38</v>
       </c>
       <c r="D170" t="s">
@@ -19886,25 +19885,25 @@
       <c r="F170">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G170" s="3" t="s">
+      <c r="G170" t="s">
         <v>34</v>
       </c>
-      <c r="H170" s="3" t="s">
+      <c r="H170" t="s">
         <v>35</v>
       </c>
-      <c r="I170" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J170" s="3" t="s">
+      <c r="I170" t="s">
+        <v>39</v>
+      </c>
+      <c r="J170" t="s">
         <v>40</v>
       </c>
       <c r="K170">
         <v>53216</v>
       </c>
-      <c r="L170" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M170" s="3" t="s">
+      <c r="L170" t="s">
+        <v>39</v>
+      </c>
+      <c r="M170" t="s">
         <v>43</v>
       </c>
       <c r="N170" s="2">
@@ -19987,7 +19986,7 @@
       <c r="B171" t="s">
         <v>37</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="C171" t="s">
         <v>38</v>
       </c>
       <c r="D171" t="s">
@@ -19999,25 +19998,25 @@
       <c r="F171">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G171" s="3" t="s">
+      <c r="G171" t="s">
         <v>34</v>
       </c>
-      <c r="H171" s="3" t="s">
+      <c r="H171" t="s">
         <v>35</v>
       </c>
-      <c r="I171" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J171" s="3" t="s">
+      <c r="I171" t="s">
+        <v>39</v>
+      </c>
+      <c r="J171" t="s">
         <v>40</v>
       </c>
       <c r="K171">
         <v>53216</v>
       </c>
-      <c r="L171" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M171" s="3" t="s">
+      <c r="L171" t="s">
+        <v>39</v>
+      </c>
+      <c r="M171" t="s">
         <v>43</v>
       </c>
       <c r="N171" s="2">
@@ -20100,7 +20099,7 @@
       <c r="B172" t="s">
         <v>37</v>
       </c>
-      <c r="C172" s="3" t="s">
+      <c r="C172" t="s">
         <v>38</v>
       </c>
       <c r="D172" t="s">
@@ -20112,25 +20111,25 @@
       <c r="F172">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G172" s="3" t="s">
+      <c r="G172" t="s">
         <v>34</v>
       </c>
-      <c r="H172" s="3" t="s">
+      <c r="H172" t="s">
         <v>35</v>
       </c>
-      <c r="I172" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J172" s="3" t="s">
+      <c r="I172" t="s">
+        <v>39</v>
+      </c>
+      <c r="J172" t="s">
         <v>40</v>
       </c>
       <c r="K172">
         <v>53216</v>
       </c>
-      <c r="L172" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M172" s="3" t="s">
+      <c r="L172" t="s">
+        <v>39</v>
+      </c>
+      <c r="M172" t="s">
         <v>43</v>
       </c>
       <c r="N172" s="2">
@@ -20213,7 +20212,7 @@
       <c r="B173" t="s">
         <v>37</v>
       </c>
-      <c r="C173" s="3" t="s">
+      <c r="C173" t="s">
         <v>38</v>
       </c>
       <c r="D173" t="s">
@@ -20225,25 +20224,25 @@
       <c r="F173">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G173" s="3" t="s">
+      <c r="G173" t="s">
         <v>34</v>
       </c>
-      <c r="H173" s="3" t="s">
+      <c r="H173" t="s">
         <v>35</v>
       </c>
-      <c r="I173" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J173" s="3" t="s">
+      <c r="I173" t="s">
+        <v>39</v>
+      </c>
+      <c r="J173" t="s">
         <v>40</v>
       </c>
       <c r="K173">
         <v>53216</v>
       </c>
-      <c r="L173" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M173" s="3" t="s">
+      <c r="L173" t="s">
+        <v>39</v>
+      </c>
+      <c r="M173" t="s">
         <v>43</v>
       </c>
       <c r="N173" s="2">
@@ -20326,7 +20325,7 @@
       <c r="B174" t="s">
         <v>37</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="C174" t="s">
         <v>38</v>
       </c>
       <c r="D174" t="s">
@@ -20338,25 +20337,25 @@
       <c r="F174">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G174" s="3" t="s">
+      <c r="G174" t="s">
         <v>34</v>
       </c>
-      <c r="H174" s="3" t="s">
+      <c r="H174" t="s">
         <v>35</v>
       </c>
-      <c r="I174" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J174" s="3" t="s">
+      <c r="I174" t="s">
+        <v>39</v>
+      </c>
+      <c r="J174" t="s">
         <v>40</v>
       </c>
       <c r="K174">
         <v>53216</v>
       </c>
-      <c r="L174" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M174" s="3" t="s">
+      <c r="L174" t="s">
+        <v>39</v>
+      </c>
+      <c r="M174" t="s">
         <v>43</v>
       </c>
       <c r="N174" s="2">
@@ -20439,7 +20438,7 @@
       <c r="B175" t="s">
         <v>37</v>
       </c>
-      <c r="C175" s="3" t="s">
+      <c r="C175" t="s">
         <v>38</v>
       </c>
       <c r="D175" t="s">
@@ -20451,25 +20450,25 @@
       <c r="F175">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="G175" t="s">
         <v>34</v>
       </c>
-      <c r="H175" s="3" t="s">
+      <c r="H175" t="s">
         <v>35</v>
       </c>
-      <c r="I175" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J175" s="3" t="s">
+      <c r="I175" t="s">
+        <v>39</v>
+      </c>
+      <c r="J175" t="s">
         <v>40</v>
       </c>
       <c r="K175">
         <v>53216</v>
       </c>
-      <c r="L175" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M175" s="3" t="s">
+      <c r="L175" t="s">
+        <v>39</v>
+      </c>
+      <c r="M175" t="s">
         <v>43</v>
       </c>
       <c r="N175" s="2">
@@ -20552,7 +20551,7 @@
       <c r="B176" t="s">
         <v>37</v>
       </c>
-      <c r="C176" s="3" t="s">
+      <c r="C176" t="s">
         <v>38</v>
       </c>
       <c r="D176" t="s">
@@ -20564,25 +20563,25 @@
       <c r="F176">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G176" s="3" t="s">
+      <c r="G176" t="s">
         <v>34</v>
       </c>
-      <c r="H176" s="3" t="s">
+      <c r="H176" t="s">
         <v>35</v>
       </c>
-      <c r="I176" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J176" s="3" t="s">
+      <c r="I176" t="s">
+        <v>39</v>
+      </c>
+      <c r="J176" t="s">
         <v>40</v>
       </c>
       <c r="K176">
         <v>53216</v>
       </c>
-      <c r="L176" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M176" s="3" t="s">
+      <c r="L176" t="s">
+        <v>39</v>
+      </c>
+      <c r="M176" t="s">
         <v>43</v>
       </c>
       <c r="N176" s="2">
@@ -20665,7 +20664,7 @@
       <c r="B177" t="s">
         <v>37</v>
       </c>
-      <c r="C177" s="3" t="s">
+      <c r="C177" t="s">
         <v>38</v>
       </c>
       <c r="D177" t="s">
@@ -20677,25 +20676,25 @@
       <c r="F177">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G177" s="3" t="s">
+      <c r="G177" t="s">
         <v>34</v>
       </c>
-      <c r="H177" s="3" t="s">
+      <c r="H177" t="s">
         <v>35</v>
       </c>
-      <c r="I177" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J177" s="3" t="s">
+      <c r="I177" t="s">
+        <v>39</v>
+      </c>
+      <c r="J177" t="s">
         <v>40</v>
       </c>
       <c r="K177">
         <v>53216</v>
       </c>
-      <c r="L177" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M177" s="3" t="s">
+      <c r="L177" t="s">
+        <v>39</v>
+      </c>
+      <c r="M177" t="s">
         <v>43</v>
       </c>
       <c r="N177" s="2">
@@ -20778,7 +20777,7 @@
       <c r="B178" t="s">
         <v>37</v>
       </c>
-      <c r="C178" s="3" t="s">
+      <c r="C178" t="s">
         <v>38</v>
       </c>
       <c r="D178" t="s">
@@ -20790,25 +20789,25 @@
       <c r="F178">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G178" s="3" t="s">
+      <c r="G178" t="s">
         <v>34</v>
       </c>
-      <c r="H178" s="3" t="s">
+      <c r="H178" t="s">
         <v>35</v>
       </c>
-      <c r="I178" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J178" s="3" t="s">
+      <c r="I178" t="s">
+        <v>39</v>
+      </c>
+      <c r="J178" t="s">
         <v>40</v>
       </c>
       <c r="K178">
         <v>53216</v>
       </c>
-      <c r="L178" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M178" s="3" t="s">
+      <c r="L178" t="s">
+        <v>39</v>
+      </c>
+      <c r="M178" t="s">
         <v>43</v>
       </c>
       <c r="N178" s="2">
@@ -20891,7 +20890,7 @@
       <c r="B179" t="s">
         <v>37</v>
       </c>
-      <c r="C179" s="3" t="s">
+      <c r="C179" t="s">
         <v>38</v>
       </c>
       <c r="D179" t="s">
@@ -20903,25 +20902,25 @@
       <c r="F179">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G179" s="3" t="s">
+      <c r="G179" t="s">
         <v>34</v>
       </c>
-      <c r="H179" s="3" t="s">
+      <c r="H179" t="s">
         <v>35</v>
       </c>
-      <c r="I179" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J179" s="3" t="s">
+      <c r="I179" t="s">
+        <v>39</v>
+      </c>
+      <c r="J179" t="s">
         <v>40</v>
       </c>
       <c r="K179">
         <v>53216</v>
       </c>
-      <c r="L179" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M179" s="3" t="s">
+      <c r="L179" t="s">
+        <v>39</v>
+      </c>
+      <c r="M179" t="s">
         <v>43</v>
       </c>
       <c r="N179" s="2">
@@ -21004,7 +21003,7 @@
       <c r="B180" t="s">
         <v>37</v>
       </c>
-      <c r="C180" s="3" t="s">
+      <c r="C180" t="s">
         <v>38</v>
       </c>
       <c r="D180" t="s">
@@ -21016,25 +21015,25 @@
       <c r="F180">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" t="s">
         <v>34</v>
       </c>
-      <c r="H180" s="3" t="s">
+      <c r="H180" t="s">
         <v>35</v>
       </c>
-      <c r="I180" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J180" s="3" t="s">
+      <c r="I180" t="s">
+        <v>39</v>
+      </c>
+      <c r="J180" t="s">
         <v>40</v>
       </c>
       <c r="K180">
         <v>53216</v>
       </c>
-      <c r="L180" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M180" s="3" t="s">
+      <c r="L180" t="s">
+        <v>39</v>
+      </c>
+      <c r="M180" t="s">
         <v>43</v>
       </c>
       <c r="N180" s="2">
@@ -21117,7 +21116,7 @@
       <c r="B181" t="s">
         <v>37</v>
       </c>
-      <c r="C181" s="3" t="s">
+      <c r="C181" t="s">
         <v>38</v>
       </c>
       <c r="D181" t="s">
@@ -21129,25 +21128,25 @@
       <c r="F181">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" t="s">
         <v>34</v>
       </c>
-      <c r="H181" s="3" t="s">
+      <c r="H181" t="s">
         <v>35</v>
       </c>
-      <c r="I181" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J181" s="3" t="s">
+      <c r="I181" t="s">
+        <v>39</v>
+      </c>
+      <c r="J181" t="s">
         <v>40</v>
       </c>
       <c r="K181">
         <v>53216</v>
       </c>
-      <c r="L181" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M181" s="3" t="s">
+      <c r="L181" t="s">
+        <v>39</v>
+      </c>
+      <c r="M181" t="s">
         <v>43</v>
       </c>
       <c r="N181" s="2">
@@ -21230,7 +21229,7 @@
       <c r="B182" t="s">
         <v>37</v>
       </c>
-      <c r="C182" s="3" t="s">
+      <c r="C182" t="s">
         <v>38</v>
       </c>
       <c r="D182" t="s">
@@ -21242,25 +21241,25 @@
       <c r="F182">
         <v>-87.977046000000001</v>
       </c>
-      <c r="G182" s="3" t="s">
+      <c r="G182" t="s">
         <v>34</v>
       </c>
-      <c r="H182" s="3" t="s">
+      <c r="H182" t="s">
         <v>35</v>
       </c>
-      <c r="I182" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J182" s="3" t="s">
+      <c r="I182" t="s">
+        <v>39</v>
+      </c>
+      <c r="J182" t="s">
         <v>40</v>
       </c>
       <c r="K182">
         <v>53216</v>
       </c>
-      <c r="L182" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M182" s="3" t="s">
+      <c r="L182" t="s">
+        <v>39</v>
+      </c>
+      <c r="M182" t="s">
         <v>43</v>
       </c>
       <c r="N182" s="2">
